--- a/sipii_caixa_20260618.xlsx
+++ b/sipii_caixa_20260618.xlsx
@@ -784,7 +784,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>2,26651300</t>
+          <t>2,26756400</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
@@ -794,12 +794,12 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>0,51</t>
+          <t>0,55</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>5,47</t>
+          <t>5,52</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
@@ -809,7 +809,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>428,126</t>
+          <t>422,073</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>5,50835500</t>
+          <t>5,51086500</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -1031,12 +1031,12 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>0,50</t>
+          <t>0,55</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>5,37</t>
+          <t>5,42</t>
         </is>
       </c>
       <c r="H3" s="5" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>6.580,399</t>
+          <t>6.589,125</t>
         </is>
       </c>
       <c r="J3" s="4" t="inlineStr">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2,78126000</t>
+          <t>2,78252800</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -1268,12 +1268,12 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>0,50</t>
+          <t>0,55</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>5,36</t>
+          <t>5,41</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>963,137</t>
+          <t>981,047</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -1496,32 +1496,32 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>3,33905500</t>
+          <t>3,34077100</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>0,053</t>
+          <t>0,051</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>0,57</t>
+          <t>0,63</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>5,97</t>
+          <t>6,02</t>
         </is>
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
-          <t>14,02</t>
+          <t>14,03</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>11,688</t>
+          <t>11,696</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
@@ -1735,22 +1735,22 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3,49394400</t>
+          <t>3,49578300</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>0,053</t>
+          <t>0,052</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>0,58</t>
+          <t>0,63</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>6,09</t>
+          <t>6,14</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
@@ -1760,7 +1760,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>119,906</t>
+          <t>119,989</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -1977,32 +1977,32 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>1.840,27428100</t>
+          <t>1.841,26242900</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>0,058</t>
+          <t>0,053</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>0,64</t>
+          <t>0,69</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>6,19</t>
+          <t>6,25</t>
         </is>
       </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
-          <t>14,61</t>
+          <t>14,64</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>96,867</t>
+          <t>96,939</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
@@ -2216,22 +2216,22 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>9,72202400</t>
+          <t>9,72663400</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>0,049</t>
+          <t>0,047</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>0,53</t>
+          <t>0,57</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>5,68</t>
+          <t>5,73</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
@@ -2241,7 +2241,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>583,225</t>
+          <t>583,143</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2455,22 +2455,22 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>3,36260500</t>
+          <t>3,36430300</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>0,052</t>
+          <t>0,050</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>0,56</t>
+          <t>0,61</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>6,05</t>
+          <t>6,10</t>
         </is>
       </c>
       <c r="H9" s="5" t="inlineStr">
@@ -2480,7 +2480,7 @@
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>63,100</t>
+          <t>63,265</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
@@ -2493,43 +2493,183 @@
           <t>https://www.caixa.gov.br/fundos-investimento/e-fundos/renda-fixa-longo-prazo</t>
         </is>
       </c>
-      <c r="L9" s="4" t="inlineStr"/>
-      <c r="M9" s="4" t="inlineStr"/>
-      <c r="N9" s="4" t="inlineStr"/>
-      <c r="O9" s="4" t="inlineStr"/>
-      <c r="P9" s="4" t="inlineStr"/>
-      <c r="Q9" s="4" t="inlineStr"/>
-      <c r="R9" s="4" t="inlineStr"/>
-      <c r="S9" s="4" t="inlineStr"/>
-      <c r="T9" s="4" t="inlineStr"/>
-      <c r="U9" s="4" t="inlineStr"/>
-      <c r="V9" s="4" t="inlineStr"/>
-      <c r="W9" s="4" t="inlineStr"/>
-      <c r="X9" s="4" t="inlineStr"/>
-      <c r="Y9" s="4" t="inlineStr"/>
-      <c r="Z9" s="4" t="inlineStr"/>
-      <c r="AA9" s="4" t="inlineStr"/>
+      <c r="L9" s="4" t="inlineStr">
+        <is>
+          <t>15.154.422/0001-99</t>
+        </is>
+      </c>
+      <c r="M9" s="4" t="inlineStr">
+        <is>
+          <t>5834</t>
+        </is>
+      </c>
+      <c r="N9" s="4" t="inlineStr">
+        <is>
+          <t>Moderado</t>
+        </is>
+      </c>
+      <c r="O9" s="4" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="P9" s="4" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="Q9" s="4" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="R9" s="4" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="S9" s="4" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="T9" s="4" t="inlineStr">
+        <is>
+          <t>D+0 (du)</t>
+        </is>
+      </c>
+      <c r="U9" s="4" t="inlineStr">
+        <is>
+          <t>D+0 (du)</t>
+        </is>
+      </c>
+      <c r="V9" s="4" t="inlineStr">
+        <is>
+          <t>D+00 (du)</t>
+        </is>
+      </c>
+      <c r="W9" s="4" t="inlineStr">
+        <is>
+          <t>CDI</t>
+        </is>
+      </c>
+      <c r="X9" s="4" t="inlineStr">
+        <is>
+          <t>RF até 49% Crédito Privado</t>
+        </is>
+      </c>
+      <c r="Y9" s="4" t="inlineStr">
+        <is>
+          <t>Aberto para captação</t>
+        </is>
+      </c>
+      <c r="Z9" s="4" t="inlineStr">
+        <is>
+          <t>LONGO PRAZO</t>
+        </is>
+      </c>
+      <c r="AA9" s="4" t="inlineStr">
+        <is>
+          <t>GERAL</t>
+        </is>
+      </c>
       <c r="AB9" s="4" t="inlineStr"/>
-      <c r="AC9" s="4" t="inlineStr"/>
-      <c r="AD9" s="4" t="inlineStr"/>
-      <c r="AE9" s="4" t="inlineStr"/>
-      <c r="AF9" s="4" t="inlineStr"/>
-      <c r="AG9" s="4" t="inlineStr"/>
-      <c r="AH9" s="4" t="inlineStr"/>
-      <c r="AI9" s="4" t="inlineStr"/>
-      <c r="AJ9" s="4" t="inlineStr"/>
+      <c r="AC9" s="4" t="inlineStr">
+        <is>
+          <t>17h00</t>
+        </is>
+      </c>
+      <c r="AD9" s="4" t="inlineStr">
+        <is>
+          <t>Sim · Automatico · 90%</t>
+        </is>
+      </c>
+      <c r="AE9" s="4" t="inlineStr">
+        <is>
+          <t>AUTOMATICO</t>
+        </is>
+      </c>
+      <c r="AF9" s="4" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="AG9" s="4" t="inlineStr">
+        <is>
+          <t>["Pessoa Física", "PJ Varejo", "Private"]</t>
+        </is>
+      </c>
+      <c r="AH9" s="4" t="inlineStr">
+        <is>
+          <t>["Pessoa Física", "PJ Varejo", "Private"]</t>
+        </is>
+      </c>
+      <c r="AI9" s="4" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="AJ9" s="4" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
       <c r="AK9" s="4" t="inlineStr"/>
-      <c r="AL9" s="4" t="inlineStr"/>
-      <c r="AM9" s="4" t="inlineStr"/>
-      <c r="AN9" s="4" t="inlineStr"/>
-      <c r="AO9" s="4" t="inlineStr"/>
-      <c r="AP9" s="4" t="inlineStr"/>
-      <c r="AQ9" s="4" t="inlineStr"/>
-      <c r="AR9" s="4" t="inlineStr"/>
-      <c r="AS9" s="4" t="inlineStr"/>
-      <c r="AT9" s="4" t="inlineStr"/>
-      <c r="AU9" s="4" t="inlineStr"/>
-      <c r="AV9" s="4" t="inlineStr"/>
+      <c r="AL9" s="4" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="AM9" s="4" t="inlineStr">
+        <is>
+          <t>CAIXA E-FUNDO FUNDO DE INVESTIMENTO EM COTAS DE CLASSE DE FUNDO DE INVESTIMENTO FINANCEIRO RENDA FIXA LONGO PRAZO - RESPONSABILIDADE LIMITADA</t>
+        </is>
+      </c>
+      <c r="AN9" s="4" t="inlineStr">
+        <is>
+          <t>Este Fundo não está adaptado às normas vigentes para RPPS (Regimes Próprios de Previdência Social).As movimentações neste Fundo são realizadas exclusivamente pelo Internet Banking.</t>
+        </is>
+      </c>
+      <c r="AO9" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_5834.pdf</t>
+        </is>
+      </c>
+      <c r="AP9" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_5834.pdf</t>
+        </is>
+      </c>
+      <c r="AQ9" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_5834.pdf</t>
+        </is>
+      </c>
+      <c r="AR9" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/FR_5834.pdf</t>
+        </is>
+      </c>
+      <c r="AS9" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5834.pdf</t>
+        </is>
+      </c>
+      <c r="AT9" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5834.pdf</t>
+        </is>
+      </c>
+      <c r="AU9" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-termos-adesao/TA_5834.pdf</t>
+        </is>
+      </c>
+      <c r="AV9" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/caixa-asset/sumario-remuneracao/Documents/sumarios/5834-SUMARIO.pdf</t>
+        </is>
+      </c>
       <c r="AW9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
@@ -2550,22 +2690,22 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>3,00313200</t>
+          <t>3,00471000</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>0,055</t>
+          <t>0,052</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>0,59</t>
+          <t>0,64</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>6,26</t>
+          <t>6,32</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
@@ -2575,7 +2715,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1.667,881</t>
+          <t>1.666,121</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -2785,32 +2925,32 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>19,80776200</t>
+          <t>19,74531100</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>-0,040</t>
+          <t>-0,315</t>
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>-0,34</t>
+          <t>-0,66</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>3,34</t>
+          <t>3,01</t>
         </is>
       </c>
       <c r="H11" s="5" t="inlineStr">
         <is>
-          <t>10,80</t>
+          <t>10,57</t>
         </is>
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>119,446</t>
+          <t>118,734</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
@@ -3028,32 +3168,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>13,45222400</t>
+          <t>13,42036500</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>-0,142</t>
+          <t>-0,236</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>-0,31</t>
+          <t>-0,55</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>4,61</t>
+          <t>4,36</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>9,74</t>
+          <t>9,52</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>27,565</t>
+          <t>27,493</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3271,22 +3411,22 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>46,23723800</t>
+          <t>46,25910400</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>0,049</t>
+          <t>0,047</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>0,52</t>
+          <t>0,57</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>5,67</t>
+          <t>5,72</t>
         </is>
       </c>
       <c r="H13" s="5" t="inlineStr">
@@ -3296,7 +3436,7 @@
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>40,553</t>
+          <t>40,573</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
@@ -3511,7 +3651,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>20,24922600</t>
+          <t>20,25874900</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
@@ -3521,12 +3661,12 @@
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>0,52</t>
+          <t>0,56</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>5,57</t>
+          <t>5,62</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
@@ -3536,7 +3676,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>64,424</t>
+          <t>64,430</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3750,32 +3890,32 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>3,13710200</t>
+          <t>3,13147200</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>-0,106</t>
+          <t>-0,179</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>-0,16</t>
+          <t>-0,34</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>5,62</t>
+          <t>5,43</t>
         </is>
       </c>
       <c r="H15" s="5" t="inlineStr">
         <is>
-          <t>11,01</t>
+          <t>10,84</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>78,017</t>
+          <t>77,877</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
@@ -3993,22 +4133,22 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>14,97936400</t>
+          <t>14,98649700</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>0,049</t>
+          <t>0,047</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>0,53</t>
+          <t>0,58</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>5,71</t>
+          <t>5,76</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
@@ -4018,7 +4158,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>27,752</t>
+          <t>27,728</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4232,22 +4372,22 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>3,00479600</t>
+          <t>3,00618300</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>0,048</t>
+          <t>0,046</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>0,51</t>
+          <t>0,56</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>5,54</t>
+          <t>5,59</t>
         </is>
       </c>
       <c r="H17" s="5" t="inlineStr">
@@ -4467,32 +4607,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3,30553800</t>
+          <t>3,29603900</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>-0,028</t>
+          <t>-0,287</t>
         </is>
       </c>
       <c r="F18" s="7" t="inlineStr">
         <is>
-          <t>-0,27</t>
+          <t>-0,56</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>3,71</t>
+          <t>3,41</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>11,37</t>
+          <t>11,16</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>134,666</t>
+          <t>134,195</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4710,22 +4850,22 @@
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>3,04603200</t>
+          <t>3,04766800</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>0,055</t>
+          <t>0,053</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>0,60</t>
+          <t>0,65</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>6,27</t>
+          <t>6,32</t>
         </is>
       </c>
       <c r="H19" s="5" t="inlineStr">
@@ -4735,7 +4875,7 @@
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>1.771,488</t>
+          <t>1.778,264</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
@@ -4941,22 +5081,22 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>32,84653000</t>
+          <t>32,86261700</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>0,051</t>
+          <t>0,048</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>0,54</t>
+          <t>0,59</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>5,87</t>
+          <t>5,92</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
@@ -4966,7 +5106,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2.199,008</t>
+          <t>2.194,540</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5180,22 +5320,22 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>3,31133300</t>
+          <t>3,31295600</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>0,051</t>
+          <t>0,049</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>0,54</t>
+          <t>0,59</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>5,88</t>
+          <t>5,93</t>
         </is>
       </c>
       <c r="H21" s="5" t="inlineStr">
@@ -5205,7 +5345,7 @@
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>13,017</t>
+          <t>13,023</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
@@ -5424,32 +5564,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>3,32861700</t>
+          <t>3,31210000</t>
         </is>
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>-0,308</t>
+          <t>-0,496</t>
         </is>
       </c>
       <c r="F22" s="7" t="inlineStr">
         <is>
-          <t>-0,59</t>
+          <t>-1,09</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>4,44</t>
+          <t>3,92</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>9,39</t>
+          <t>8,73</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>65,288</t>
+          <t>64,947</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5663,22 +5803,22 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>19,07348100</t>
+          <t>19,08342200</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>0,053</t>
+          <t>0,052</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>0,57</t>
+          <t>0,62</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>6,03</t>
+          <t>6,08</t>
         </is>
       </c>
       <c r="H23" s="5" t="inlineStr">
@@ -5688,7 +5828,7 @@
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>950,853</t>
+          <t>951,524</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
@@ -5902,17 +6042,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1,11391100</t>
+          <t>1,11389616</t>
         </is>
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
-          <t>-0,055</t>
+          <t>-0,001</t>
         </is>
       </c>
       <c r="F24" s="7" t="inlineStr">
         <is>
-          <t>-0,04</t>
+          <t>-0,05</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
@@ -5927,7 +6067,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>205,529</t>
+          <t>205,399</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6137,12 +6277,12 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>1,24367200</t>
-        </is>
-      </c>
-      <c r="E25" s="5" t="inlineStr">
-        <is>
-          <t>0,055</t>
+          <t>1,24365400</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>-0,001</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
@@ -6157,12 +6297,12 @@
       </c>
       <c r="H25" s="5" t="inlineStr">
         <is>
-          <t>14,61</t>
+          <t>14,53</t>
         </is>
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>71,413</t>
+          <t>71,486</t>
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr">
@@ -6368,32 +6508,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>1.836,46763400</t>
+          <t>1.837,47806500</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>0,058</t>
+          <t>0,055</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>0,63</t>
+          <t>0,69</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>6,27</t>
+          <t>6,33</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>14,79</t>
+          <t>14,81</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>176,083</t>
+          <t>176,591</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6607,32 +6747,32 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>1,20257500</t>
+          <t>1,20140100</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>-0,108</t>
+          <t>-0,097</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>0,21</t>
+          <t>0,12</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>7,00</t>
+          <t>6,90</t>
         </is>
       </c>
       <c r="H27" s="5" t="inlineStr">
         <is>
-          <t>13,55</t>
+          <t>13,40</t>
         </is>
       </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>39,954</t>
+          <t>39,915</t>
         </is>
       </c>
       <c r="J27" s="4" t="inlineStr">
@@ -6846,12 +6986,12 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>1,04234000</t>
-        </is>
-      </c>
-      <c r="E28" s="3" t="inlineStr">
-        <is>
-          <t>0,068</t>
+          <t>1,04231500</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>-0,002</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
@@ -6861,7 +7001,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>6,30</t>
+          <t>6,29</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -6871,7 +7011,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>22,019</t>
+          <t>22,029</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7069,12 +7209,12 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>1,17384200</t>
-        </is>
-      </c>
-      <c r="E29" s="5" t="inlineStr">
-        <is>
-          <t>0,059</t>
+          <t>1,17382500</t>
+        </is>
+      </c>
+      <c r="E29" s="6" t="inlineStr">
+        <is>
+          <t>-0,001</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
@@ -7089,12 +7229,12 @@
       </c>
       <c r="H29" s="5" t="inlineStr">
         <is>
-          <t>14,05</t>
+          <t>14,00</t>
         </is>
       </c>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>66,360</t>
+          <t>66,361</t>
         </is>
       </c>
       <c r="J29" s="4" t="inlineStr">
@@ -7300,12 +7440,12 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1,07985700</t>
-        </is>
-      </c>
-      <c r="E30" s="3" t="inlineStr">
-        <is>
-          <t>0,135</t>
+          <t>1,07984177</t>
+        </is>
+      </c>
+      <c r="E30" s="7" t="inlineStr">
+        <is>
+          <t>-0,001</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
@@ -7325,7 +7465,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>305,220</t>
+          <t>305,062</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7754,32 +7894,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>5,15154900</t>
+          <t>5,15438100</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>0,055</t>
+          <t>0,054</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>0,60</t>
+          <t>0,65</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>6,25</t>
+          <t>6,31</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>14,76</t>
+          <t>14,77</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>852,054</t>
+          <t>852,113</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7993,22 +8133,22 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>4,95682100</t>
+          <t>4,95948900</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>0,056</t>
+          <t>0,053</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>0,60</t>
+          <t>0,66</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>6,26</t>
+          <t>6,32</t>
         </is>
       </c>
       <c r="H33" s="5" t="inlineStr">
@@ -8018,7 +8158,7 @@
       </c>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>3.275,900</t>
+          <t>3.278,556</t>
         </is>
       </c>
       <c r="J33" s="4" t="inlineStr">
@@ -8232,7 +8372,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>29,30678400</t>
+          <t>29,32093300</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
@@ -8242,12 +8382,12 @@
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>0,53</t>
+          <t>0,58</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>5,67</t>
+          <t>5,73</t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
@@ -8257,7 +8397,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>21,132</t>
+          <t>21,042</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8459,22 +8599,22 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>30,68124200</t>
+          <t>30,69754300</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>0,054</t>
+          <t>0,053</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>0,58</t>
+          <t>0,64</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>6,15</t>
+          <t>6,20</t>
         </is>
       </c>
       <c r="H35" s="5" t="inlineStr">
@@ -8484,7 +8624,7 @@
       </c>
       <c r="I35" s="4" t="inlineStr">
         <is>
-          <t>3.110,596</t>
+          <t>3.113,721</t>
         </is>
       </c>
       <c r="J35" s="4" t="inlineStr">
@@ -8694,22 +8834,22 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>1.773,40944400</t>
+          <t>1.773,64955900</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>0,021</t>
+          <t>0,013</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>0,26</t>
+          <t>0,27</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>5,28</t>
+          <t>5,29</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
@@ -8719,7 +8859,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>122,998</t>
+          <t>123,004</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -8929,7 +9069,7 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>3,22985300</t>
+          <t>3,23156600</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -8939,22 +9079,22 @@
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>0,58</t>
+          <t>0,64</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>6,28</t>
+          <t>6,34</t>
         </is>
       </c>
       <c r="H37" s="5" t="inlineStr">
         <is>
-          <t>14,67</t>
+          <t>14,66</t>
         </is>
       </c>
       <c r="I37" s="4" t="inlineStr">
         <is>
-          <t>588,131</t>
+          <t>589,556</t>
         </is>
       </c>
       <c r="J37" s="4" t="inlineStr">
@@ -9168,32 +9308,32 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>6,20254000</t>
+          <t>6,20578100</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>0,053</t>
+          <t>0,052</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>0,57</t>
+          <t>0,63</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>6,04</t>
+          <t>6,10</t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>14,16</t>
+          <t>14,17</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>121,546</t>
+          <t>121,597</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -9408,22 +9548,22 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1,27237400</t>
+          <t>1,27307100</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>0,057</t>
+          <t>0,054</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>0,61</t>
+          <t>0,67</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>6,37</t>
+          <t>6,43</t>
         </is>
       </c>
       <c r="H39" s="5" t="inlineStr">
@@ -9433,7 +9573,7 @@
       </c>
       <c r="I39" s="4" t="inlineStr">
         <is>
-          <t>395,614</t>
+          <t>399,576</t>
         </is>
       </c>
       <c r="J39" s="4" t="inlineStr">
@@ -9647,32 +9787,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>10,61925800</t>
+          <t>10,62497800</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>0,054</t>
+          <t>0,053</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>0,59</t>
+          <t>0,64</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>6,23</t>
+          <t>6,29</t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>14,62</t>
+          <t>14,63</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>2.373,006</t>
+          <t>2.373,743</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -9886,7 +10026,7 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>5,53047300</t>
+          <t>5,53354200</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -9896,12 +10036,12 @@
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>0,59</t>
+          <t>0,65</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>6,33</t>
+          <t>6,39</t>
         </is>
       </c>
       <c r="H41" s="5" t="inlineStr">
@@ -9911,7 +10051,7 @@
       </c>
       <c r="I41" s="4" t="inlineStr">
         <is>
-          <t>545,955</t>
+          <t>546,267</t>
         </is>
       </c>
       <c r="J41" s="4" t="inlineStr">
@@ -10126,22 +10266,22 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>3,57690900</t>
+          <t>3,57886300</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>0,057</t>
+          <t>0,054</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>0,61</t>
+          <t>0,67</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>6,35</t>
+          <t>6,41</t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
@@ -10151,7 +10291,7 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>15.562,574</t>
+          <t>15.615,617</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -10374,7 +10514,7 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>5,31567100</t>
+          <t>5,31854500</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -10384,12 +10524,12 @@
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>0,59</t>
+          <t>0,65</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>6,40</t>
+          <t>6,45</t>
         </is>
       </c>
       <c r="H43" s="5" t="inlineStr">
@@ -10399,7 +10539,7 @@
       </c>
       <c r="I43" s="4" t="inlineStr">
         <is>
-          <t>1.474,914</t>
+          <t>1.475,202</t>
         </is>
       </c>
       <c r="J43" s="4" t="inlineStr">
@@ -10614,7 +10754,7 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>30,39570500</t>
+          <t>30,41007400</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
@@ -10624,22 +10764,22 @@
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>0,52</t>
+          <t>0,57</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>5,63</t>
+          <t>5,68</t>
         </is>
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t>13,14</t>
+          <t>13,13</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>164,274</t>
+          <t>164,313</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -11084,22 +11224,22 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>2,81452700</t>
+          <t>2,81585000</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>0,046</t>
+          <t>0,047</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>0,51</t>
+          <t>0,56</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>5,55</t>
+          <t>5,60</t>
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr">
@@ -11109,7 +11249,7 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>5.930,645</t>
+          <t>5.932,273</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -11321,32 +11461,32 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>3,61351700</t>
+          <t>3,61539400</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
         <is>
-          <t>0,053</t>
+          <t>0,051</t>
         </is>
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>0,58</t>
+          <t>0,63</t>
         </is>
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
-          <t>6,09</t>
+          <t>6,14</t>
         </is>
       </c>
       <c r="H47" s="5" t="inlineStr">
         <is>
-          <t>14,26</t>
+          <t>14,27</t>
         </is>
       </c>
       <c r="I47" s="4" t="inlineStr">
         <is>
-          <t>2.216,790</t>
+          <t>2.218,514</t>
         </is>
       </c>
       <c r="J47" s="4" t="inlineStr">
@@ -11564,7 +11704,7 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>1,29368500</t>
+          <t>1,29436400</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
@@ -11574,12 +11714,12 @@
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>0,58</t>
+          <t>0,63</t>
         </is>
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>6,25</t>
+          <t>6,30</t>
         </is>
       </c>
       <c r="H48" s="3" t="inlineStr">
@@ -11589,7 +11729,7 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>64,901</t>
+          <t>64,270</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -11803,22 +11943,22 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>9,70814200</t>
+          <t>9,71322100</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
-          <t>0,053</t>
+          <t>0,052</t>
         </is>
       </c>
       <c r="F49" s="5" t="inlineStr">
         <is>
-          <t>0,58</t>
+          <t>0,64</t>
         </is>
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
-          <t>6,13</t>
+          <t>6,19</t>
         </is>
       </c>
       <c r="H49" s="5" t="inlineStr">
@@ -11828,7 +11968,7 @@
       </c>
       <c r="I49" s="4" t="inlineStr">
         <is>
-          <t>829,308</t>
+          <t>828,700</t>
         </is>
       </c>
       <c r="J49" s="4" t="inlineStr">
@@ -12047,7 +12187,7 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>4,46709000</t>
+          <t>4,46941000</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
@@ -12057,12 +12197,12 @@
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>0,57</t>
+          <t>0,62</t>
         </is>
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>6,18</t>
+          <t>6,23</t>
         </is>
       </c>
       <c r="H50" s="3" t="inlineStr">
@@ -12072,7 +12212,7 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>16.098,874</t>
+          <t>16.136,315</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -12294,22 +12434,22 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>4,78603700</t>
+          <t>4,78859800</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
         <is>
-          <t>0,055</t>
+          <t>0,053</t>
         </is>
       </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
-          <t>0,60</t>
+          <t>0,65</t>
         </is>
       </c>
       <c r="G51" s="5" t="inlineStr">
         <is>
-          <t>6,27</t>
+          <t>6,33</t>
         </is>
       </c>
       <c r="H51" s="5" t="inlineStr">
@@ -12319,7 +12459,7 @@
       </c>
       <c r="I51" s="4" t="inlineStr">
         <is>
-          <t>9.452,417</t>
+          <t>9.465,010</t>
         </is>
       </c>
       <c r="J51" s="4" t="inlineStr">
@@ -12537,32 +12677,32 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>5,11422300</t>
+          <t>5,11696400</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>0,054</t>
+          <t>0,053</t>
         </is>
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>0,60</t>
+          <t>0,65</t>
         </is>
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>6,30</t>
+          <t>6,35</t>
         </is>
       </c>
       <c r="H52" s="3" t="inlineStr">
         <is>
-          <t>14,76</t>
+          <t>14,77</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>21.220,897</t>
+          <t>21.266,527</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -12784,22 +12924,22 @@
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>3,19449100</t>
+          <t>3,19622000</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
         <is>
-          <t>0,055</t>
+          <t>0,054</t>
         </is>
       </c>
       <c r="F53" s="5" t="inlineStr">
         <is>
-          <t>0,60</t>
+          <t>0,66</t>
         </is>
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>6,35</t>
+          <t>6,40</t>
         </is>
       </c>
       <c r="H53" s="5" t="inlineStr">
@@ -12809,7 +12949,7 @@
       </c>
       <c r="I53" s="4" t="inlineStr">
         <is>
-          <t>13.703,341</t>
+          <t>13.709,452</t>
         </is>
       </c>
       <c r="J53" s="4" t="inlineStr">
@@ -13031,7 +13171,7 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>1.733,91750100</t>
+          <t>1.734,80595100</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
@@ -13041,12 +13181,12 @@
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>0,56</t>
+          <t>0,61</t>
         </is>
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>6,02</t>
+          <t>6,08</t>
         </is>
       </c>
       <c r="H54" s="3" t="inlineStr">
@@ -13056,7 +13196,7 @@
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>248,604</t>
+          <t>250,070</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -13126,12 +13266,12 @@
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>1,41959400</t>
-        </is>
-      </c>
-      <c r="E55" s="5" t="inlineStr">
-        <is>
-          <t>0,055</t>
+          <t>1,41959100</t>
+        </is>
+      </c>
+      <c r="E55" s="4" t="inlineStr">
+        <is>
+          <t>0,000</t>
         </is>
       </c>
       <c r="F55" s="5" t="inlineStr">
@@ -13146,7 +13286,7 @@
       </c>
       <c r="H55" s="5" t="inlineStr">
         <is>
-          <t>14,37</t>
+          <t>14,33</t>
         </is>
       </c>
       <c r="I55" s="4" t="inlineStr">
@@ -13357,17 +13497,17 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>1.217,72962800</t>
-        </is>
-      </c>
-      <c r="E56" s="3" t="inlineStr">
-        <is>
-          <t>0,365</t>
+          <t>1.217,69392000</t>
+        </is>
+      </c>
+      <c r="E56" s="7" t="inlineStr">
+        <is>
+          <t>-0,002</t>
         </is>
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t>1,17</t>
+          <t>1,16</t>
         </is>
       </c>
       <c r="G56" s="7" t="inlineStr">
@@ -13377,12 +13517,12 @@
       </c>
       <c r="H56" s="3" t="inlineStr">
         <is>
-          <t>2,73</t>
+          <t>3,15</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>37,115</t>
+          <t>37,114</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -13606,32 +13746,32 @@
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>12,50481800</t>
+          <t>12,46506100</t>
         </is>
       </c>
       <c r="E57" s="6" t="inlineStr">
         <is>
-          <t>-0,220</t>
+          <t>-0,317</t>
         </is>
       </c>
       <c r="F57" s="6" t="inlineStr">
         <is>
-          <t>-0,66</t>
+          <t>-0,97</t>
         </is>
       </c>
       <c r="G57" s="5" t="inlineStr">
         <is>
-          <t>5,34</t>
+          <t>5,00</t>
         </is>
       </c>
       <c r="H57" s="5" t="inlineStr">
         <is>
-          <t>15,73</t>
+          <t>15,47</t>
         </is>
       </c>
       <c r="I57" s="4" t="inlineStr">
         <is>
-          <t>322,067</t>
+          <t>540,035</t>
         </is>
       </c>
       <c r="J57" s="4" t="inlineStr">
@@ -13849,32 +13989,32 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>1.629,90381800</t>
+          <t>1.623,76337600</t>
         </is>
       </c>
       <c r="E58" s="7" t="inlineStr">
         <is>
-          <t>-0,228</t>
+          <t>-0,376</t>
         </is>
       </c>
       <c r="F58" s="7" t="inlineStr">
         <is>
-          <t>-0,44</t>
+          <t>-0,82</t>
         </is>
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>4,01</t>
+          <t>3,62</t>
         </is>
       </c>
       <c r="H58" s="3" t="inlineStr">
         <is>
-          <t>11,85</t>
+          <t>11,40</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>113,924</t>
+          <t>113,482</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -14084,32 +14224,32 @@
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>2.420,46868400</t>
-        </is>
-      </c>
-      <c r="E59" s="6" t="inlineStr">
-        <is>
-          <t>-0,394</t>
-        </is>
-      </c>
-      <c r="F59" s="6" t="inlineStr">
-        <is>
-          <t>-0,09</t>
+          <t>2.428,38644500</t>
+        </is>
+      </c>
+      <c r="E59" s="5" t="inlineStr">
+        <is>
+          <t>0,327</t>
+        </is>
+      </c>
+      <c r="F59" s="5" t="inlineStr">
+        <is>
+          <t>0,23</t>
         </is>
       </c>
       <c r="G59" s="5" t="inlineStr">
         <is>
-          <t>17,83</t>
+          <t>18,22</t>
         </is>
       </c>
       <c r="H59" s="5" t="inlineStr">
         <is>
-          <t>31,86</t>
+          <t>32,36</t>
         </is>
       </c>
       <c r="I59" s="4" t="inlineStr">
         <is>
-          <t>13,409</t>
+          <t>13,448</t>
         </is>
       </c>
       <c r="J59" s="4" t="inlineStr">
@@ -14546,12 +14686,12 @@
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>1,25334900</t>
-        </is>
-      </c>
-      <c r="E61" s="5" t="inlineStr">
-        <is>
-          <t>0,064</t>
+          <t>1,25327900</t>
+        </is>
+      </c>
+      <c r="E61" s="6" t="inlineStr">
+        <is>
+          <t>-0,005</t>
         </is>
       </c>
       <c r="F61" s="5" t="inlineStr">
@@ -14561,17 +14701,17 @@
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
-          <t>2,62</t>
+          <t>2,61</t>
         </is>
       </c>
       <c r="H61" s="5" t="inlineStr">
         <is>
-          <t>10,15</t>
+          <t>9,97</t>
         </is>
       </c>
       <c r="I61" s="4" t="inlineStr">
         <is>
-          <t>6,313</t>
+          <t>6,312</t>
         </is>
       </c>
       <c r="J61" s="4" t="inlineStr">
@@ -14781,32 +14921,32 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>1,11864200</t>
+          <t>1,11206400</t>
         </is>
       </c>
       <c r="E62" s="7" t="inlineStr">
         <is>
-          <t>-0,700</t>
+          <t>-0,588</t>
         </is>
       </c>
       <c r="F62" s="7" t="inlineStr">
         <is>
-          <t>-1,71</t>
+          <t>-2,29</t>
         </is>
       </c>
       <c r="G62" s="7" t="inlineStr">
         <is>
-          <t>-3,52</t>
+          <t>-4,08</t>
         </is>
       </c>
       <c r="H62" s="3" t="inlineStr">
         <is>
-          <t>9,90</t>
+          <t>9,49</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>3,585</t>
+          <t>3,565</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
@@ -15243,27 +15383,27 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>1,39964100</t>
+          <t>1,39957100</t>
         </is>
       </c>
       <c r="E64" s="7" t="inlineStr">
         <is>
-          <t>-0,144</t>
+          <t>-0,005</t>
         </is>
       </c>
       <c r="F64" s="7" t="inlineStr">
         <is>
-          <t>-1,45</t>
+          <t>-1,46</t>
         </is>
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>2,53</t>
+          <t>2,52</t>
         </is>
       </c>
       <c r="H64" s="3" t="inlineStr">
         <is>
-          <t>14,53</t>
+          <t>14,41</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
@@ -15705,32 +15845,32 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>1,11655200</t>
-        </is>
-      </c>
-      <c r="E66" s="3" t="inlineStr">
-        <is>
-          <t>0,627</t>
-        </is>
-      </c>
-      <c r="F66" s="3" t="inlineStr">
-        <is>
-          <t>0,54</t>
+          <t>1,10713800</t>
+        </is>
+      </c>
+      <c r="E66" s="7" t="inlineStr">
+        <is>
+          <t>-0,843</t>
+        </is>
+      </c>
+      <c r="F66" s="7" t="inlineStr">
+        <is>
+          <t>-0,30</t>
         </is>
       </c>
       <c r="G66" s="7" t="inlineStr">
         <is>
-          <t>-7,39</t>
+          <t>-8,17</t>
         </is>
       </c>
       <c r="H66" s="7" t="inlineStr">
         <is>
-          <t>-5,47</t>
+          <t>-5,64</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>3,718</t>
+          <t>3,776</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
@@ -15940,32 +16080,32 @@
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>5,31853100</t>
+          <t>5,30470760</t>
         </is>
       </c>
       <c r="E67" s="6" t="inlineStr">
         <is>
-          <t>-0,170</t>
+          <t>-0,259</t>
         </is>
       </c>
       <c r="F67" s="6" t="inlineStr">
         <is>
-          <t>-0,34</t>
+          <t>-0,60</t>
         </is>
       </c>
       <c r="G67" s="5" t="inlineStr">
         <is>
-          <t>3,65</t>
+          <t>3,38</t>
         </is>
       </c>
       <c r="H67" s="5" t="inlineStr">
         <is>
-          <t>11,69</t>
+          <t>11,36</t>
         </is>
       </c>
       <c r="I67" s="4" t="inlineStr">
         <is>
-          <t>32,651</t>
+          <t>32,535</t>
         </is>
       </c>
       <c r="J67" s="4" t="inlineStr">
@@ -16179,32 +16319,32 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>4,54411100</t>
+          <t>4,57496800</t>
         </is>
       </c>
       <c r="E68" s="3" t="inlineStr">
         <is>
-          <t>0,083</t>
+          <t>0,679</t>
         </is>
       </c>
       <c r="F68" s="7" t="inlineStr">
         <is>
-          <t>-4,57</t>
+          <t>-3,92</t>
         </is>
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>2,27</t>
+          <t>2,96</t>
         </is>
       </c>
       <c r="H68" s="3" t="inlineStr">
         <is>
-          <t>34,45</t>
+          <t>35,71</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>567,649</t>
+          <t>570,691</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
@@ -16418,12 +16558,12 @@
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>2,85529000</t>
+          <t>2,85516400</t>
         </is>
       </c>
       <c r="E69" s="6" t="inlineStr">
         <is>
-          <t>-0,117</t>
+          <t>-0,004</t>
         </is>
       </c>
       <c r="F69" s="6" t="inlineStr">
@@ -16438,12 +16578,12 @@
       </c>
       <c r="H69" s="5" t="inlineStr">
         <is>
-          <t>9,54</t>
+          <t>9,67</t>
         </is>
       </c>
       <c r="I69" s="4" t="inlineStr">
         <is>
-          <t>73,586</t>
+          <t>73,582</t>
         </is>
       </c>
       <c r="J69" s="4" t="inlineStr">
@@ -16653,32 +16793,32 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>1.689,77060300</t>
+          <t>1.696,75800500</t>
         </is>
       </c>
       <c r="E70" s="3" t="inlineStr">
         <is>
-          <t>0,244</t>
+          <t>0,413</t>
         </is>
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
-          <t>1,56</t>
+          <t>1,98</t>
         </is>
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>7,25</t>
+          <t>7,69</t>
         </is>
       </c>
       <c r="H70" s="3" t="inlineStr">
         <is>
-          <t>13,36</t>
+          <t>13,70</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>29,679</t>
+          <t>29,796</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
@@ -16892,32 +17032,32 @@
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>3,80957300</t>
+          <t>3,76377800</t>
         </is>
       </c>
       <c r="E71" s="6" t="inlineStr">
         <is>
-          <t>-0,469</t>
+          <t>-1,202</t>
         </is>
       </c>
       <c r="F71" s="6" t="inlineStr">
         <is>
-          <t>-0,49</t>
+          <t>-1,69</t>
         </is>
       </c>
       <c r="G71" s="5" t="inlineStr">
         <is>
-          <t>13,24</t>
+          <t>11,88</t>
         </is>
       </c>
       <c r="H71" s="5" t="inlineStr">
         <is>
-          <t>35,86</t>
+          <t>35,24</t>
         </is>
       </c>
       <c r="I71" s="4" t="inlineStr">
         <is>
-          <t>2.372,165</t>
+          <t>2.344,183</t>
         </is>
       </c>
       <c r="J71" s="4" t="inlineStr">
@@ -17131,22 +17271,22 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>1,90943800</t>
+          <t>1,90972700</t>
         </is>
       </c>
       <c r="E72" s="3" t="inlineStr">
         <is>
-          <t>0,016</t>
+          <t>0,015</t>
         </is>
       </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
-          <t>0,24</t>
+          <t>0,26</t>
         </is>
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>5,03</t>
+          <t>5,05</t>
         </is>
       </c>
       <c r="H72" s="3" t="inlineStr">
@@ -17370,32 +17510,32 @@
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>1.651,77540600</t>
+          <t>1.645,56436200</t>
         </is>
       </c>
       <c r="E73" s="6" t="inlineStr">
         <is>
-          <t>-0,226</t>
+          <t>-0,376</t>
         </is>
       </c>
       <c r="F73" s="6" t="inlineStr">
         <is>
-          <t>-0,39</t>
+          <t>-0,77</t>
         </is>
       </c>
       <c r="G73" s="5" t="inlineStr">
         <is>
-          <t>4,44</t>
+          <t>4,05</t>
         </is>
       </c>
       <c r="H73" s="5" t="inlineStr">
         <is>
-          <t>12,82</t>
+          <t>12,37</t>
         </is>
       </c>
       <c r="I73" s="4" t="inlineStr">
         <is>
-          <t>14,394</t>
+          <t>14,333</t>
         </is>
       </c>
       <c r="J73" s="4" t="inlineStr">
@@ -17605,12 +17745,12 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>0,47587800</t>
+          <t>0,47585034</t>
         </is>
       </c>
       <c r="E74" s="7" t="inlineStr">
         <is>
-          <t>-0,981</t>
+          <t>-0,005</t>
         </is>
       </c>
       <c r="F74" s="7" t="inlineStr">
@@ -17620,7 +17760,7 @@
       </c>
       <c r="G74" s="7" t="inlineStr">
         <is>
-          <t>-34,09</t>
+          <t>-34,10</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -17847,32 +17987,32 @@
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>3,27155200</t>
+          <t>3,28148000</t>
         </is>
       </c>
       <c r="E75" s="5" t="inlineStr">
         <is>
-          <t>0,095</t>
-        </is>
-      </c>
-      <c r="F75" s="6" t="inlineStr">
-        <is>
-          <t>-0,25</t>
+          <t>0,303</t>
+        </is>
+      </c>
+      <c r="F75" s="5" t="inlineStr">
+        <is>
+          <t>0,04</t>
         </is>
       </c>
       <c r="G75" s="5" t="inlineStr">
         <is>
-          <t>2,68</t>
+          <t>2,99</t>
         </is>
       </c>
       <c r="H75" s="5" t="inlineStr">
         <is>
-          <t>7,89</t>
+          <t>8,57</t>
         </is>
       </c>
       <c r="I75" s="4" t="inlineStr">
         <is>
-          <t>155,819</t>
+          <t>156,292</t>
         </is>
       </c>
       <c r="J75" s="4" t="inlineStr">
@@ -18092,32 +18232,32 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>1,53744800</t>
+          <t>1,53156200</t>
         </is>
       </c>
       <c r="E76" s="7" t="inlineStr">
         <is>
-          <t>-0,115</t>
+          <t>-0,382</t>
         </is>
       </c>
       <c r="F76" s="7" t="inlineStr">
         <is>
-          <t>-0,75</t>
+          <t>-1,13</t>
         </is>
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>2,96</t>
+          <t>2,57</t>
         </is>
       </c>
       <c r="H76" s="3" t="inlineStr">
         <is>
-          <t>18,73</t>
+          <t>18,44</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>14,484</t>
+          <t>14,428</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
@@ -18337,32 +18477,32 @@
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>1,38258800</t>
+          <t>1,38268200</t>
         </is>
       </c>
       <c r="E77" s="5" t="inlineStr">
         <is>
-          <t>0,235</t>
+          <t>0,006</t>
         </is>
       </c>
       <c r="F77" s="5" t="inlineStr">
         <is>
-          <t>0,63</t>
+          <t>0,64</t>
         </is>
       </c>
       <c r="G77" s="5" t="inlineStr">
         <is>
-          <t>1,94</t>
+          <t>1,95</t>
         </is>
       </c>
       <c r="H77" s="5" t="inlineStr">
         <is>
-          <t>6,46</t>
+          <t>7,06</t>
         </is>
       </c>
       <c r="I77" s="4" t="inlineStr">
         <is>
-          <t>70,850</t>
+          <t>70,855</t>
         </is>
       </c>
       <c r="J77" s="4" t="inlineStr">
@@ -18584,32 +18724,32 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>1,48188800</t>
-        </is>
-      </c>
-      <c r="E78" s="3" t="inlineStr">
-        <is>
-          <t>0,457</t>
+          <t>1,47054700</t>
+        </is>
+      </c>
+      <c r="E78" s="7" t="inlineStr">
+        <is>
+          <t>-0,765</t>
         </is>
       </c>
       <c r="F78" s="7" t="inlineStr">
         <is>
-          <t>-1,34</t>
+          <t>-2,10</t>
         </is>
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>2,47</t>
+          <t>1,68</t>
         </is>
       </c>
       <c r="H78" s="3" t="inlineStr">
         <is>
-          <t>14,15</t>
+          <t>13,29</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>192,142</t>
+          <t>190,672</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
@@ -18831,12 +18971,12 @@
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>1,78973900</t>
-        </is>
-      </c>
-      <c r="E79" s="5" t="inlineStr">
-        <is>
-          <t>0,047</t>
+          <t>1,78970300</t>
+        </is>
+      </c>
+      <c r="E79" s="6" t="inlineStr">
+        <is>
+          <t>-0,002</t>
         </is>
       </c>
       <c r="F79" s="5" t="inlineStr">
@@ -18851,12 +18991,12 @@
       </c>
       <c r="H79" s="5" t="inlineStr">
         <is>
-          <t>10,13</t>
+          <t>10,46</t>
         </is>
       </c>
       <c r="I79" s="4" t="inlineStr">
         <is>
-          <t>175,775</t>
+          <t>175,379</t>
         </is>
       </c>
       <c r="J79" s="4" t="inlineStr">
@@ -19066,32 +19206,32 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>5,61245200</t>
+          <t>5,59747900</t>
         </is>
       </c>
       <c r="E80" s="7" t="inlineStr">
         <is>
-          <t>-0,129</t>
+          <t>-0,266</t>
         </is>
       </c>
       <c r="F80" s="7" t="inlineStr">
         <is>
-          <t>-0,01</t>
+          <t>-0,28</t>
         </is>
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>5,33</t>
+          <t>5,05</t>
         </is>
       </c>
       <c r="H80" s="3" t="inlineStr">
         <is>
-          <t>13,80</t>
+          <t>13,45</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>896,822</t>
+          <t>894,105</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
@@ -19305,22 +19445,22 @@
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>3,65941100</t>
+          <t>3,66001900</t>
         </is>
       </c>
       <c r="E81" s="5" t="inlineStr">
         <is>
-          <t>0,018</t>
+          <t>0,016</t>
         </is>
       </c>
       <c r="F81" s="5" t="inlineStr">
         <is>
-          <t>0,26</t>
+          <t>0,27</t>
         </is>
       </c>
       <c r="G81" s="5" t="inlineStr">
         <is>
-          <t>5,21</t>
+          <t>5,22</t>
         </is>
       </c>
       <c r="H81" s="5" t="inlineStr">
@@ -19330,7 +19470,7 @@
       </c>
       <c r="I81" s="4" t="inlineStr">
         <is>
-          <t>745,958</t>
+          <t>744,650</t>
         </is>
       </c>
       <c r="J81" s="4" t="inlineStr">
@@ -19540,12 +19680,12 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>6,82102000</t>
+          <t>6,82073900</t>
         </is>
       </c>
       <c r="E82" s="7" t="inlineStr">
         <is>
-          <t>-0,172</t>
+          <t>-0,004</t>
         </is>
       </c>
       <c r="F82" s="7" t="inlineStr">
@@ -19560,12 +19700,12 @@
       </c>
       <c r="H82" s="3" t="inlineStr">
         <is>
-          <t>15,93</t>
+          <t>15,77</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>128,857</t>
+          <t>128,764</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
@@ -19775,7 +19915,7 @@
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>1,43776600</t>
+          <t>1,44032600</t>
         </is>
       </c>
       <c r="E83" s="6" t="inlineStr">
@@ -19785,22 +19925,22 @@
       </c>
       <c r="F83" s="5" t="inlineStr">
         <is>
-          <t>0,77</t>
+          <t>0,95</t>
         </is>
       </c>
       <c r="G83" s="5" t="inlineStr">
         <is>
-          <t>4,36</t>
+          <t>4,54</t>
         </is>
       </c>
       <c r="H83" s="5" t="inlineStr">
         <is>
-          <t>16,04</t>
+          <t>16,08</t>
         </is>
       </c>
       <c r="I83" s="4" t="inlineStr">
         <is>
-          <t>284,675</t>
+          <t>285,215</t>
         </is>
       </c>
       <c r="J83" s="4" t="inlineStr">
@@ -20015,17 +20155,17 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>1,35361800</t>
+          <t>1,35358900</t>
         </is>
       </c>
       <c r="E84" s="7" t="inlineStr">
         <is>
-          <t>-0,495</t>
+          <t>-0,002</t>
         </is>
       </c>
       <c r="F84" s="3" t="inlineStr">
         <is>
-          <t>2,31</t>
+          <t>2,30</t>
         </is>
       </c>
       <c r="G84" s="3" t="inlineStr">
@@ -20035,12 +20175,12 @@
       </c>
       <c r="H84" s="3" t="inlineStr">
         <is>
-          <t>5,31</t>
+          <t>5,02</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>13,024</t>
+          <t>12,825</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
@@ -20254,32 +20394,32 @@
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>3,79960300</t>
-        </is>
-      </c>
-      <c r="E85" s="5" t="inlineStr">
-        <is>
-          <t>0,498</t>
+          <t>3,79095200</t>
+        </is>
+      </c>
+      <c r="E85" s="6" t="inlineStr">
+        <is>
+          <t>-0,227</t>
         </is>
       </c>
       <c r="F85" s="5" t="inlineStr">
         <is>
-          <t>1,10</t>
+          <t>0,87</t>
         </is>
       </c>
       <c r="G85" s="6" t="inlineStr">
         <is>
-          <t>-5,47</t>
+          <t>-5,69</t>
         </is>
       </c>
       <c r="H85" s="6" t="inlineStr">
         <is>
-          <t>-3,15</t>
+          <t>-3,52</t>
         </is>
       </c>
       <c r="I85" s="4" t="inlineStr">
         <is>
-          <t>96,258</t>
+          <t>96,029</t>
         </is>
       </c>
       <c r="J85" s="4" t="inlineStr">
@@ -20493,32 +20633,32 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>6,58269500</t>
+          <t>6,55830700</t>
         </is>
       </c>
       <c r="E86" s="7" t="inlineStr">
         <is>
-          <t>-0,364</t>
+          <t>-0,370</t>
         </is>
       </c>
       <c r="F86" s="7" t="inlineStr">
         <is>
-          <t>-0,73</t>
+          <t>-1,10</t>
         </is>
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>3,78</t>
+          <t>3,40</t>
         </is>
       </c>
       <c r="H86" s="3" t="inlineStr">
         <is>
-          <t>17,72</t>
+          <t>17,23</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>323,575</t>
+          <t>322,369</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
@@ -20732,32 +20872,32 @@
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>2,52431300</t>
+          <t>2,50692100</t>
         </is>
       </c>
       <c r="E87" s="6" t="inlineStr">
         <is>
-          <t>-0,443</t>
+          <t>-0,688</t>
         </is>
       </c>
       <c r="F87" s="6" t="inlineStr">
         <is>
-          <t>-2,35</t>
+          <t>-3,02</t>
         </is>
       </c>
       <c r="G87" s="5" t="inlineStr">
         <is>
-          <t>4,91</t>
+          <t>4,19</t>
         </is>
       </c>
       <c r="H87" s="5" t="inlineStr">
         <is>
-          <t>20,84</t>
+          <t>20,35</t>
         </is>
       </c>
       <c r="I87" s="4" t="inlineStr">
         <is>
-          <t>13,013</t>
+          <t>12,922</t>
         </is>
       </c>
       <c r="J87" s="4" t="inlineStr">
@@ -20971,32 +21111,32 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>1.859,31897300</t>
+          <t>1.837,22718300</t>
         </is>
       </c>
       <c r="E88" s="7" t="inlineStr">
         <is>
-          <t>-1,069</t>
+          <t>-1,188</t>
         </is>
       </c>
       <c r="F88" s="7" t="inlineStr">
         <is>
-          <t>-3,65</t>
+          <t>-4,80</t>
         </is>
       </c>
       <c r="G88" s="7" t="inlineStr">
         <is>
-          <t>-6,33</t>
+          <t>-7,45</t>
         </is>
       </c>
       <c r="H88" s="3" t="inlineStr">
         <is>
-          <t>7,65</t>
+          <t>6,60</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>9,499</t>
+          <t>9,387</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr">
@@ -21199,32 +21339,32 @@
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>10,07561900</t>
+          <t>10,01278800</t>
         </is>
       </c>
       <c r="E89" s="6" t="inlineStr">
         <is>
-          <t>-0,370</t>
+          <t>-0,623</t>
         </is>
       </c>
       <c r="F89" s="6" t="inlineStr">
         <is>
-          <t>-1,74</t>
+          <t>-2,35</t>
         </is>
       </c>
       <c r="G89" s="5" t="inlineStr">
         <is>
-          <t>1,75</t>
+          <t>1,12</t>
         </is>
       </c>
       <c r="H89" s="5" t="inlineStr">
         <is>
-          <t>20,90</t>
+          <t>20,73</t>
         </is>
       </c>
       <c r="I89" s="4" t="inlineStr">
         <is>
-          <t>277,144</t>
+          <t>275,128</t>
         </is>
       </c>
       <c r="J89" s="4" t="inlineStr">
@@ -21438,32 +21578,32 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>1,41808800</t>
+          <t>1,39732600</t>
         </is>
       </c>
       <c r="E90" s="7" t="inlineStr">
         <is>
-          <t>-0,958</t>
+          <t>-1,464</t>
         </is>
       </c>
       <c r="F90" s="7" t="inlineStr">
         <is>
-          <t>-3,63</t>
+          <t>-5,04</t>
         </is>
       </c>
       <c r="G90" s="7" t="inlineStr">
         <is>
-          <t>-6,97</t>
+          <t>-8,33</t>
         </is>
       </c>
       <c r="H90" s="7" t="inlineStr">
         <is>
-          <t>-3,52</t>
+          <t>-4,36</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>429,739</t>
+          <t>423,437</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
@@ -21677,32 +21817,32 @@
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>1,07843000</t>
+          <t>1,05805400</t>
         </is>
       </c>
       <c r="E91" s="6" t="inlineStr">
         <is>
-          <t>-0,329</t>
+          <t>-1,889</t>
         </is>
       </c>
       <c r="F91" s="6" t="inlineStr">
         <is>
-          <t>-2,69</t>
+          <t>-4,53</t>
         </is>
       </c>
       <c r="G91" s="6" t="inlineStr">
         <is>
-          <t>-7,34</t>
+          <t>-9,09</t>
         </is>
       </c>
       <c r="H91" s="6" t="inlineStr">
         <is>
-          <t>-4,78</t>
+          <t>-6,09</t>
         </is>
       </c>
       <c r="I91" s="4" t="inlineStr">
         <is>
-          <t>55,348</t>
+          <t>54,298</t>
         </is>
       </c>
       <c r="J91" s="4" t="inlineStr">
@@ -21916,32 +22056,32 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>1,65994200</t>
+          <t>1,64144100</t>
         </is>
       </c>
       <c r="E92" s="7" t="inlineStr">
         <is>
-          <t>-0,718</t>
+          <t>-1,114</t>
         </is>
       </c>
       <c r="F92" s="7" t="inlineStr">
         <is>
-          <t>-2,84</t>
+          <t>-3,93</t>
         </is>
       </c>
       <c r="G92" s="7" t="inlineStr">
         <is>
-          <t>-2,61</t>
+          <t>-3,70</t>
         </is>
       </c>
       <c r="H92" s="3" t="inlineStr">
         <is>
-          <t>5,05</t>
+          <t>4,10</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>2,050</t>
+          <t>2,027</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
@@ -22155,32 +22295,32 @@
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>4,24986400</t>
+          <t>4,22611700</t>
         </is>
       </c>
       <c r="E93" s="6" t="inlineStr">
         <is>
-          <t>-0,940</t>
+          <t>-0,558</t>
         </is>
       </c>
       <c r="F93" s="6" t="inlineStr">
         <is>
-          <t>-5,80</t>
+          <t>-6,33</t>
         </is>
       </c>
       <c r="G93" s="5" t="inlineStr">
         <is>
-          <t>34,95</t>
+          <t>34,20</t>
         </is>
       </c>
       <c r="H93" s="5" t="inlineStr">
         <is>
-          <t>31,13</t>
+          <t>26,77</t>
         </is>
       </c>
       <c r="I93" s="4" t="inlineStr">
         <is>
-          <t>71,098</t>
+          <t>70,689</t>
         </is>
       </c>
       <c r="J93" s="4" t="inlineStr">
@@ -22394,32 +22534,32 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>8,45508300</t>
+          <t>8,39652500</t>
         </is>
       </c>
       <c r="E94" s="7" t="inlineStr">
         <is>
-          <t>-0,446</t>
+          <t>-0,692</t>
         </is>
       </c>
       <c r="F94" s="7" t="inlineStr">
         <is>
-          <t>-2,40</t>
+          <t>-3,07</t>
         </is>
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>4,42</t>
+          <t>3,70</t>
         </is>
       </c>
       <c r="H94" s="3" t="inlineStr">
         <is>
-          <t>19,55</t>
+          <t>19,07</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>84,356</t>
+          <t>83,717</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
@@ -22633,32 +22773,32 @@
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>1,23155100</t>
+          <t>1,23120600</t>
         </is>
       </c>
       <c r="E95" s="6" t="inlineStr">
         <is>
-          <t>-0,537</t>
+          <t>-0,028</t>
         </is>
       </c>
       <c r="F95" s="6" t="inlineStr">
         <is>
-          <t>-3,08</t>
+          <t>-3,10</t>
         </is>
       </c>
       <c r="G95" s="6" t="inlineStr">
         <is>
-          <t>-4,31</t>
+          <t>-4,34</t>
         </is>
       </c>
       <c r="H95" s="5" t="inlineStr">
         <is>
-          <t>3,17</t>
+          <t>3,44</t>
         </is>
       </c>
       <c r="I95" s="4" t="inlineStr">
         <is>
-          <t>278,321</t>
+          <t>278,241</t>
         </is>
       </c>
       <c r="J95" s="4" t="inlineStr">
@@ -22872,32 +23012,32 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>1,83689300</t>
-        </is>
-      </c>
-      <c r="E96" s="3" t="inlineStr">
-        <is>
-          <t>0,372</t>
+          <t>1,78857600</t>
+        </is>
+      </c>
+      <c r="E96" s="7" t="inlineStr">
+        <is>
+          <t>-2,630</t>
         </is>
       </c>
       <c r="F96" s="7" t="inlineStr">
         <is>
-          <t>-1,32</t>
+          <t>-3,92</t>
         </is>
       </c>
       <c r="G96" s="7" t="inlineStr">
         <is>
-          <t>-3,39</t>
+          <t>-5,93</t>
         </is>
       </c>
       <c r="H96" s="3" t="inlineStr">
         <is>
-          <t>15,66</t>
+          <t>12,79</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>111,827</t>
+          <t>108,878</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
@@ -23111,32 +23251,32 @@
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>2,79565200</t>
+          <t>2,75524800</t>
         </is>
       </c>
       <c r="E97" s="6" t="inlineStr">
         <is>
-          <t>-0,785</t>
+          <t>-1,445</t>
         </is>
       </c>
       <c r="F97" s="6" t="inlineStr">
         <is>
-          <t>-3,36</t>
+          <t>-4,75</t>
         </is>
       </c>
       <c r="G97" s="5" t="inlineStr">
         <is>
-          <t>2,57</t>
+          <t>1,09</t>
         </is>
       </c>
       <c r="H97" s="5" t="inlineStr">
         <is>
-          <t>10,45</t>
+          <t>8,62</t>
         </is>
       </c>
       <c r="I97" s="4" t="inlineStr">
         <is>
-          <t>122,175</t>
+          <t>120,395</t>
         </is>
       </c>
       <c r="J97" s="4" t="inlineStr">
@@ -23350,32 +23490,32 @@
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>1,80622000</t>
+          <t>1,78472600</t>
         </is>
       </c>
       <c r="E98" s="7" t="inlineStr">
         <is>
-          <t>-1,071</t>
+          <t>-1,189</t>
         </is>
       </c>
       <c r="F98" s="7" t="inlineStr">
         <is>
-          <t>-3,70</t>
+          <t>-4,84</t>
         </is>
       </c>
       <c r="G98" s="7" t="inlineStr">
         <is>
-          <t>-6,77</t>
+          <t>-7,88</t>
         </is>
       </c>
       <c r="H98" s="3" t="inlineStr">
         <is>
-          <t>6,45</t>
+          <t>5,41</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>47,605</t>
+          <t>47,037</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr">
@@ -23593,32 +23733,32 @@
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>6,00132400</t>
-        </is>
-      </c>
-      <c r="E99" s="6" t="inlineStr">
-        <is>
-          <t>-1,292</t>
+          <t>6,00636200</t>
+        </is>
+      </c>
+      <c r="E99" s="5" t="inlineStr">
+        <is>
+          <t>0,083</t>
         </is>
       </c>
       <c r="F99" s="6" t="inlineStr">
         <is>
-          <t>-6,50</t>
+          <t>-6,43</t>
         </is>
       </c>
       <c r="G99" s="5" t="inlineStr">
         <is>
-          <t>27,95</t>
+          <t>28,05</t>
         </is>
       </c>
       <c r="H99" s="5" t="inlineStr">
         <is>
-          <t>28,61</t>
+          <t>25,95</t>
         </is>
       </c>
       <c r="I99" s="4" t="inlineStr">
         <is>
-          <t>108,617</t>
+          <t>108,421</t>
         </is>
       </c>
       <c r="J99" s="4" t="inlineStr">
@@ -23832,7 +23972,7 @@
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>1.224,97730400</t>
+          <t>1.225,53744500</t>
         </is>
       </c>
       <c r="E100" s="3" t="inlineStr">
@@ -23842,22 +23982,22 @@
       </c>
       <c r="F100" s="7" t="inlineStr">
         <is>
-          <t>-3,77</t>
+          <t>-3,72</t>
         </is>
       </c>
       <c r="G100" s="7" t="inlineStr">
         <is>
-          <t>-10,38</t>
+          <t>-10,34</t>
         </is>
       </c>
       <c r="H100" s="7" t="inlineStr">
         <is>
-          <t>-10,86</t>
+          <t>-10,49</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>40,060</t>
+          <t>40,229</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr">
@@ -24071,32 +24211,32 @@
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>38,51738400</t>
-        </is>
-      </c>
-      <c r="E101" s="5" t="inlineStr">
-        <is>
-          <t>0,336</t>
+          <t>37,73146400</t>
+        </is>
+      </c>
+      <c r="E101" s="6" t="inlineStr">
+        <is>
+          <t>-2,040</t>
         </is>
       </c>
       <c r="F101" s="6" t="inlineStr">
         <is>
-          <t>-1,74</t>
+          <t>-3,75</t>
         </is>
       </c>
       <c r="G101" s="5" t="inlineStr">
         <is>
-          <t>11,49</t>
+          <t>9,21</t>
         </is>
       </c>
       <c r="H101" s="5" t="inlineStr">
         <is>
-          <t>59,96</t>
+          <t>64,06</t>
         </is>
       </c>
       <c r="I101" s="4" t="inlineStr">
         <is>
-          <t>647,240</t>
+          <t>633,941</t>
         </is>
       </c>
       <c r="J101" s="4" t="inlineStr">
@@ -24310,32 +24450,32 @@
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>2,83809700</t>
+          <t>2,88035300</t>
         </is>
       </c>
       <c r="E102" s="3" t="inlineStr">
         <is>
-          <t>0,159</t>
+          <t>1,488</t>
         </is>
       </c>
       <c r="F102" s="3" t="inlineStr">
         <is>
-          <t>5,73</t>
+          <t>7,30</t>
         </is>
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>17,16</t>
+          <t>18,90</t>
         </is>
       </c>
       <c r="H102" s="3" t="inlineStr">
         <is>
-          <t>37,87</t>
+          <t>41,84</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>468,875</t>
+          <t>475,825</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr">
@@ -24553,32 +24693,32 @@
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>4,70658400</t>
+          <t>4,66748600</t>
         </is>
       </c>
       <c r="E103" s="6" t="inlineStr">
         <is>
-          <t>-0,409</t>
+          <t>-0,830</t>
         </is>
       </c>
       <c r="F103" s="6" t="inlineStr">
         <is>
-          <t>-2,14</t>
+          <t>-2,96</t>
         </is>
       </c>
       <c r="G103" s="5" t="inlineStr">
         <is>
-          <t>4,87</t>
+          <t>4,00</t>
         </is>
       </c>
       <c r="H103" s="5" t="inlineStr">
         <is>
-          <t>21,96</t>
+          <t>21,28</t>
         </is>
       </c>
       <c r="I103" s="4" t="inlineStr">
         <is>
-          <t>22,752</t>
+          <t>22,559</t>
         </is>
       </c>
       <c r="J103" s="4" t="inlineStr">
@@ -24792,32 +24932,32 @@
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>1.471,51503200</t>
+          <t>1.467,99756100</t>
         </is>
       </c>
       <c r="E104" s="7" t="inlineStr">
         <is>
-          <t>-0,079</t>
+          <t>-0,239</t>
         </is>
       </c>
       <c r="F104" s="7" t="inlineStr">
         <is>
-          <t>-2,15</t>
+          <t>-2,38</t>
         </is>
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>1,11</t>
+          <t>0,87</t>
         </is>
       </c>
       <c r="H104" s="3" t="inlineStr">
         <is>
-          <t>14,09</t>
+          <t>13,26</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>29,226</t>
+          <t>29,162</t>
         </is>
       </c>
       <c r="J104" s="2" t="inlineStr">
@@ -25031,32 +25171,32 @@
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>1,88438800</t>
+          <t>1,86441000</t>
         </is>
       </c>
       <c r="E105" s="6" t="inlineStr">
         <is>
-          <t>-0,907</t>
+          <t>-1,060</t>
         </is>
       </c>
       <c r="F105" s="6" t="inlineStr">
         <is>
-          <t>-2,69</t>
+          <t>-3,72</t>
         </is>
       </c>
       <c r="G105" s="6" t="inlineStr">
         <is>
-          <t>-7,37</t>
+          <t>-8,35</t>
         </is>
       </c>
       <c r="H105" s="5" t="inlineStr">
         <is>
-          <t>4,18</t>
+          <t>3,10</t>
         </is>
       </c>
       <c r="I105" s="4" t="inlineStr">
         <is>
-          <t>1,698</t>
+          <t>1,680</t>
         </is>
       </c>
       <c r="J105" s="4" t="inlineStr">
@@ -25262,32 +25402,32 @@
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>5,70076600</t>
+          <t>5,66291400</t>
         </is>
       </c>
       <c r="E106" s="7" t="inlineStr">
         <is>
-          <t>-0,477</t>
+          <t>-0,663</t>
         </is>
       </c>
       <c r="F106" s="7" t="inlineStr">
         <is>
-          <t>-2,80</t>
+          <t>-3,45</t>
         </is>
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>5,97</t>
+          <t>5,27</t>
         </is>
       </c>
       <c r="H106" s="3" t="inlineStr">
         <is>
-          <t>22,34</t>
+          <t>21,80</t>
         </is>
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>41,927</t>
+          <t>41,649</t>
         </is>
       </c>
       <c r="J106" s="2" t="inlineStr">
@@ -25493,32 +25633,32 @@
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>2,16223600</t>
+          <t>2,14348300</t>
         </is>
       </c>
       <c r="E107" s="6" t="inlineStr">
         <is>
-          <t>-0,708</t>
+          <t>-0,867</t>
         </is>
       </c>
       <c r="F107" s="6" t="inlineStr">
         <is>
-          <t>-2,26</t>
+          <t>-3,11</t>
         </is>
       </c>
       <c r="G107" s="5" t="inlineStr">
         <is>
-          <t>3,05</t>
+          <t>2,15</t>
         </is>
       </c>
       <c r="H107" s="5" t="inlineStr">
         <is>
-          <t>19,56</t>
+          <t>18,91</t>
         </is>
       </c>
       <c r="I107" s="4" t="inlineStr">
         <is>
-          <t>34,419</t>
+          <t>34,159</t>
         </is>
       </c>
       <c r="J107" s="4" t="inlineStr">
@@ -25732,32 +25872,32 @@
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>39,42043100</t>
+          <t>39,20033600</t>
         </is>
       </c>
       <c r="E108" s="7" t="inlineStr">
         <is>
-          <t>-0,940</t>
+          <t>-0,558</t>
         </is>
       </c>
       <c r="F108" s="7" t="inlineStr">
         <is>
-          <t>-5,79</t>
+          <t>-6,32</t>
         </is>
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>35,02</t>
+          <t>34,27</t>
         </is>
       </c>
       <c r="H108" s="3" t="inlineStr">
         <is>
-          <t>31,25</t>
+          <t>26,89</t>
         </is>
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t>776,420</t>
+          <t>770,594</t>
         </is>
       </c>
       <c r="J108" s="2" t="inlineStr">
@@ -25971,32 +26111,32 @@
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>0,82860700</t>
+          <t>0,81799300</t>
         </is>
       </c>
       <c r="E109" s="6" t="inlineStr">
         <is>
-          <t>-0,509</t>
+          <t>-1,280</t>
         </is>
       </c>
       <c r="F109" s="6" t="inlineStr">
         <is>
-          <t>-3,60</t>
+          <t>-4,83</t>
         </is>
       </c>
       <c r="G109" s="6" t="inlineStr">
         <is>
-          <t>-13,91</t>
+          <t>-15,02</t>
         </is>
       </c>
       <c r="H109" s="6" t="inlineStr">
         <is>
-          <t>-22,62</t>
+          <t>-22,34</t>
         </is>
       </c>
       <c r="I109" s="4" t="inlineStr">
         <is>
-          <t>2,844</t>
+          <t>2,809</t>
         </is>
       </c>
       <c r="J109" s="4" t="inlineStr">
@@ -26206,32 +26346,32 @@
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>1,20037600</t>
-        </is>
-      </c>
-      <c r="E110" s="3" t="inlineStr">
-        <is>
-          <t>0,118</t>
-        </is>
-      </c>
-      <c r="F110" s="3" t="inlineStr">
-        <is>
-          <t>0,45</t>
+          <t>1,18003900</t>
+        </is>
+      </c>
+      <c r="E110" s="7" t="inlineStr">
+        <is>
+          <t>-1,694</t>
+        </is>
+      </c>
+      <c r="F110" s="7" t="inlineStr">
+        <is>
+          <t>-1,24</t>
         </is>
       </c>
       <c r="G110" s="7" t="inlineStr">
         <is>
-          <t>-0,80</t>
+          <t>-2,48</t>
         </is>
       </c>
       <c r="H110" s="3" t="inlineStr">
         <is>
-          <t>13,05</t>
+          <t>12,33</t>
         </is>
       </c>
       <c r="I110" s="2" t="inlineStr">
         <is>
-          <t>3,712</t>
+          <t>3,647</t>
         </is>
       </c>
       <c r="J110" s="2" t="inlineStr">
@@ -26441,32 +26581,32 @@
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>1,40191800</t>
+          <t>1,42279200</t>
         </is>
       </c>
       <c r="E111" s="5" t="inlineStr">
         <is>
-          <t>0,158</t>
+          <t>1,488</t>
         </is>
       </c>
       <c r="F111" s="5" t="inlineStr">
         <is>
-          <t>5,71</t>
+          <t>7,29</t>
         </is>
       </c>
       <c r="G111" s="5" t="inlineStr">
         <is>
-          <t>17,07</t>
+          <t>18,82</t>
         </is>
       </c>
       <c r="H111" s="5" t="inlineStr">
         <is>
-          <t>37,67</t>
+          <t>41,64</t>
         </is>
       </c>
       <c r="I111" s="4" t="inlineStr">
         <is>
-          <t>20,721</t>
+          <t>21,019</t>
         </is>
       </c>
       <c r="J111" s="4" t="inlineStr">
@@ -26481,12 +26621,12 @@
       </c>
       <c r="L111" s="4" t="inlineStr">
         <is>
-          <t>30.068.049/0001-47</t>
+          <t>59.815.671/0001-53</t>
         </is>
       </c>
       <c r="M111" s="4" t="inlineStr">
         <is>
-          <t>6499</t>
+          <t>7971</t>
         </is>
       </c>
       <c r="N111" s="4" t="inlineStr">
@@ -26521,14 +26661,14 @@
       </c>
       <c r="T111" s="4" t="inlineStr">
         <is>
+          <t>D+0 (du)</t>
+        </is>
+      </c>
+      <c r="U111" s="4" t="inlineStr">
+        <is>
           <t>D+1 (du)</t>
         </is>
       </c>
-      <c r="U111" s="4" t="inlineStr">
-        <is>
-          <t>D+1 (du)</t>
-        </is>
-      </c>
       <c r="V111" s="4" t="inlineStr">
         <is>
           <t>D+03 (du)</t>
@@ -26536,7 +26676,7 @@
       </c>
       <c r="W111" s="4" t="inlineStr">
         <is>
-          <t>IBOV</t>
+          <t>NÃO SE APLICA</t>
         </is>
       </c>
       <c r="X111" s="4" t="inlineStr">
@@ -26546,7 +26686,7 @@
       </c>
       <c r="Y111" s="4" t="inlineStr">
         <is>
-          <t>Aberto para captação</t>
+          <t>Fechado para captação</t>
         </is>
       </c>
       <c r="Z111" s="4" t="inlineStr">
@@ -26571,27 +26711,23 @@
       </c>
       <c r="AD111" s="4" t="inlineStr">
         <is>
-          <t>Sim · Automatico · 100%</t>
+          <t>Não se aplica</t>
         </is>
       </c>
       <c r="AE111" s="4" t="inlineStr">
         <is>
-          <t>AUTOMATICO</t>
-        </is>
-      </c>
-      <c r="AF111" s="4" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
+          <t>NÃO SE APLICA</t>
+        </is>
+      </c>
+      <c r="AF111" s="4" t="inlineStr"/>
       <c r="AG111" s="4" t="inlineStr">
         <is>
-          <t>["GOV", "Institucional", "Pessoa Física", "PJ Atacado", "PJ Varejo", "Private"]</t>
+          <t>["GOV", "Pessoa Física", "PJ Atacado", "Private"]</t>
         </is>
       </c>
       <c r="AH111" s="4" t="inlineStr">
         <is>
-          <t>["GOV", "Institucional", "Pessoa Física", "PJ Atacado", "PJ Varejo", "Private"]</t>
+          <t>["GOV", "Pessoa Física", "PJ Atacado", "Private"]</t>
         </is>
       </c>
       <c r="AI111" s="4" t="inlineStr">
@@ -26606,7 +26742,7 @@
       </c>
       <c r="AK111" s="4" t="inlineStr">
         <is>
-          <t>2021-06-13T00:00:00Z</t>
+          <t>2025-05-04T00:00:00Z</t>
         </is>
       </c>
       <c r="AL111" s="4" t="inlineStr">
@@ -26616,52 +26752,52 @@
       </c>
       <c r="AM111" s="4" t="inlineStr">
         <is>
-          <t>CAIXA SEGURIDADE FUNDO DE INVESTIMENTO FINANCEIRO EM AÇÕES - RESPONSABILIDADE LIMITADA</t>
+          <t>CAIXA SEGURIDADE II FUNDO DE INVESTIMENTO FINANCEIRO AÇÕES - RESPONSABILIDADE LIMITADA</t>
         </is>
       </c>
       <c r="AN111" s="4" t="inlineStr">
         <is>
-          <t>Canal de distribuição: Rede CAIXA, IBC. A reserva inicial, no âmbito da OFERTA, será feita por meio do Home Broker CAIXA. Resgates: Lock up de 45 dias. Inicio dia 30/04/2021 - Termino 13/06/2021. Liberado resgate a partir do dia 14/06/2021 (segunda-feira).</t>
+          <t>Fundo ficará fechado para novas aplicações a partir do dia 13/05/2025 (inclusive).</t>
         </is>
       </c>
       <c r="AO111" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_6499.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_7971.pdf</t>
         </is>
       </c>
       <c r="AP111" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_6499.pdf</t>
+          <t>http://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_7971.pdf</t>
         </is>
       </c>
       <c r="AQ111" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_6499.pdf</t>
+          <t>http://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_7971.pdf</t>
         </is>
       </c>
       <c r="AR111" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_6499.pdf</t>
+          <t>http://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/FR_7971.pdf</t>
         </is>
       </c>
       <c r="AS111" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_6499.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_7971.pdf</t>
         </is>
       </c>
       <c r="AT111" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_6499.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_7971.pdf</t>
         </is>
       </c>
       <c r="AU111" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-termos-adesao/TA_6499.pdf</t>
+          <t>http://www.caixa.gov.br/Downloads/aplicacao-financeira-termos-adesao/TA_7971.pdf</t>
         </is>
       </c>
       <c r="AV111" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/caixa-asset/sumario-remuneracao/Documents/sumarios/6499-SUMARIO.pdf</t>
+          <t>http://www.caixa.gov.br/caixa-asset/sumario-remuneracao/Documents/sumarios/7971-SUMARIO.pdf</t>
         </is>
       </c>
       <c r="AW111" s="4" t="inlineStr"/>
@@ -26684,32 +26820,32 @@
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>1,80103200</t>
-        </is>
-      </c>
-      <c r="E112" s="3" t="inlineStr">
-        <is>
-          <t>0,292</t>
-        </is>
-      </c>
-      <c r="F112" s="3" t="inlineStr">
-        <is>
-          <t>1,41</t>
+          <t>1,77493000</t>
+        </is>
+      </c>
+      <c r="E112" s="7" t="inlineStr">
+        <is>
+          <t>-1,449</t>
+        </is>
+      </c>
+      <c r="F112" s="7" t="inlineStr">
+        <is>
+          <t>-0,05</t>
         </is>
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>4,77</t>
+          <t>3,25</t>
         </is>
       </c>
       <c r="H112" s="3" t="inlineStr">
         <is>
-          <t>70,11</t>
+          <t>69,02</t>
         </is>
       </c>
       <c r="I112" s="2" t="inlineStr">
         <is>
-          <t>274,352</t>
+          <t>270,313</t>
         </is>
       </c>
       <c r="J112" s="2" t="inlineStr">
@@ -26927,12 +27063,12 @@
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>976,60273900</t>
+          <t>976,56786000</t>
         </is>
       </c>
       <c r="E113" s="6" t="inlineStr">
         <is>
-          <t>-0,431</t>
+          <t>-0,003</t>
         </is>
       </c>
       <c r="F113" s="6" t="inlineStr">
@@ -26947,7 +27083,7 @@
       </c>
       <c r="H113" s="5" t="inlineStr">
         <is>
-          <t>13,26</t>
+          <t>13,18</t>
         </is>
       </c>
       <c r="I113" s="4" t="inlineStr">
@@ -27166,17 +27302,17 @@
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>1.458,80592500</t>
+          <t>1.458,76648600</t>
         </is>
       </c>
       <c r="E114" s="7" t="inlineStr">
         <is>
-          <t>-0,548</t>
+          <t>-0,002</t>
         </is>
       </c>
       <c r="F114" s="7" t="inlineStr">
         <is>
-          <t>-2,43</t>
+          <t>-2,44</t>
         </is>
       </c>
       <c r="G114" s="7" t="inlineStr">
@@ -27186,7 +27322,7 @@
       </c>
       <c r="H114" s="3" t="inlineStr">
         <is>
-          <t>6,91</t>
+          <t>6,64</t>
         </is>
       </c>
       <c r="I114" s="2" t="inlineStr">
@@ -27401,32 +27537,32 @@
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>165,64717500</t>
+          <t>164,50441206</t>
         </is>
       </c>
       <c r="E115" s="6" t="inlineStr">
         <is>
-          <t>-0,441</t>
+          <t>-0,689</t>
         </is>
       </c>
       <c r="F115" s="6" t="inlineStr">
         <is>
-          <t>-2,30</t>
+          <t>-2,98</t>
         </is>
       </c>
       <c r="G115" s="5" t="inlineStr">
         <is>
-          <t>5,12</t>
+          <t>4,39</t>
         </is>
       </c>
       <c r="H115" s="5" t="inlineStr">
         <is>
-          <t>21,40</t>
+          <t>20,92</t>
         </is>
       </c>
       <c r="I115" s="4" t="inlineStr">
         <is>
-          <t>41,413</t>
+          <t>41,127</t>
         </is>
       </c>
       <c r="J115" s="4" t="inlineStr">
@@ -27640,32 +27776,32 @@
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>1,84013100</t>
-        </is>
-      </c>
-      <c r="E116" s="3" t="inlineStr">
-        <is>
-          <t>0,297</t>
-        </is>
-      </c>
-      <c r="F116" s="3" t="inlineStr">
-        <is>
-          <t>1,36</t>
+          <t>1,81364800</t>
+        </is>
+      </c>
+      <c r="E116" s="7" t="inlineStr">
+        <is>
+          <t>-1,439</t>
+        </is>
+      </c>
+      <c r="F116" s="7" t="inlineStr">
+        <is>
+          <t>-0,09</t>
         </is>
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>4,80</t>
+          <t>3,29</t>
         </is>
       </c>
       <c r="H116" s="3" t="inlineStr">
         <is>
-          <t>70,38</t>
+          <t>69,31</t>
         </is>
       </c>
       <c r="I116" s="2" t="inlineStr">
         <is>
-          <t>5,028</t>
+          <t>4,956</t>
         </is>
       </c>
       <c r="J116" s="2" t="inlineStr">
@@ -27876,32 +28012,32 @@
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>1,79452700</t>
-        </is>
-      </c>
-      <c r="E117" s="5" t="inlineStr">
-        <is>
-          <t>0,300</t>
-        </is>
-      </c>
-      <c r="F117" s="5" t="inlineStr">
-        <is>
-          <t>1,38</t>
+          <t>1,76859200</t>
+        </is>
+      </c>
+      <c r="E117" s="6" t="inlineStr">
+        <is>
+          <t>-1,445</t>
+        </is>
+      </c>
+      <c r="F117" s="6" t="inlineStr">
+        <is>
+          <t>-0,08</t>
         </is>
       </c>
       <c r="G117" s="5" t="inlineStr">
         <is>
-          <t>4,82</t>
+          <t>3,31</t>
         </is>
       </c>
       <c r="H117" s="5" t="inlineStr">
         <is>
-          <t>70,44</t>
+          <t>69,35</t>
         </is>
       </c>
       <c r="I117" s="4" t="inlineStr">
         <is>
-          <t>1.631,044</t>
+          <t>1.606,952</t>
         </is>
       </c>
       <c r="J117" s="4" t="inlineStr">
@@ -28108,32 +28244,32 @@
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>43,85957100</t>
+          <t>43,61472300</t>
         </is>
       </c>
       <c r="E118" s="7" t="inlineStr">
         <is>
-          <t>-0,940</t>
+          <t>-0,558</t>
         </is>
       </c>
       <c r="F118" s="7" t="inlineStr">
         <is>
-          <t>-5,78</t>
+          <t>-6,30</t>
         </is>
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>35,42</t>
+          <t>34,66</t>
         </is>
       </c>
       <c r="H118" s="3" t="inlineStr">
         <is>
-          <t>31,98</t>
+          <t>27,60</t>
         </is>
       </c>
       <c r="I118" s="2" t="inlineStr">
         <is>
-          <t>631,944</t>
+          <t>628,242</t>
         </is>
       </c>
       <c r="J118" s="2" t="inlineStr">
@@ -28331,32 +28467,32 @@
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
-          <t>42,68400600</t>
-        </is>
-      </c>
-      <c r="E119" s="5" t="inlineStr">
-        <is>
-          <t>0,339</t>
+          <t>41,81365500</t>
+        </is>
+      </c>
+      <c r="E119" s="6" t="inlineStr">
+        <is>
+          <t>-2,039</t>
         </is>
       </c>
       <c r="F119" s="6" t="inlineStr">
         <is>
-          <t>-1,72</t>
+          <t>-3,72</t>
         </is>
       </c>
       <c r="G119" s="5" t="inlineStr">
         <is>
-          <t>11,75</t>
+          <t>9,47</t>
         </is>
       </c>
       <c r="H119" s="5" t="inlineStr">
         <is>
-          <t>60,83</t>
+          <t>64,96</t>
         </is>
       </c>
       <c r="I119" s="4" t="inlineStr">
         <is>
-          <t>767,086</t>
+          <t>751,170</t>
         </is>
       </c>
       <c r="J119" s="4" t="inlineStr">
@@ -28554,32 +28690,32 @@
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>15,91918800</t>
+          <t>15,75605200</t>
         </is>
       </c>
       <c r="E120" s="7" t="inlineStr">
         <is>
-          <t>-1,096</t>
+          <t>-1,024</t>
         </is>
       </c>
       <c r="F120" s="7" t="inlineStr">
         <is>
-          <t>-3,23</t>
+          <t>-4,22</t>
         </is>
       </c>
       <c r="G120" s="7" t="inlineStr">
         <is>
-          <t>-5,61</t>
+          <t>-6,58</t>
         </is>
       </c>
       <c r="H120" s="3" t="inlineStr">
         <is>
-          <t>8,83</t>
+          <t>7,93</t>
         </is>
       </c>
       <c r="I120" s="2" t="inlineStr">
         <is>
-          <t>109,618</t>
+          <t>108,469</t>
         </is>
       </c>
       <c r="J120" s="2" t="inlineStr">
@@ -28786,32 +28922,32 @@
       </c>
       <c r="D121" s="4" t="inlineStr">
         <is>
-          <t>35,76966300</t>
-        </is>
-      </c>
-      <c r="E121" s="5" t="inlineStr">
-        <is>
-          <t>0,336</t>
+          <t>35,03928600</t>
+        </is>
+      </c>
+      <c r="E121" s="6" t="inlineStr">
+        <is>
+          <t>-2,041</t>
         </is>
       </c>
       <c r="F121" s="6" t="inlineStr">
         <is>
-          <t>-1,77</t>
+          <t>-3,78</t>
         </is>
       </c>
       <c r="G121" s="5" t="inlineStr">
         <is>
-          <t>11,47</t>
+          <t>9,19</t>
         </is>
       </c>
       <c r="H121" s="5" t="inlineStr">
         <is>
-          <t>59,67</t>
+          <t>63,74</t>
         </is>
       </c>
       <c r="I121" s="4" t="inlineStr">
         <is>
-          <t>12,144</t>
+          <t>11,896</t>
         </is>
       </c>
       <c r="J121" s="4" t="inlineStr">
@@ -29014,32 +29150,32 @@
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>38,74693800</t>
+          <t>38,53034500</t>
         </is>
       </c>
       <c r="E122" s="7" t="inlineStr">
         <is>
-          <t>-0,940</t>
+          <t>-0,558</t>
         </is>
       </c>
       <c r="F122" s="7" t="inlineStr">
         <is>
-          <t>-5,79</t>
+          <t>-6,31</t>
         </is>
       </c>
       <c r="G122" s="3" t="inlineStr">
         <is>
-          <t>35,14</t>
+          <t>34,39</t>
         </is>
       </c>
       <c r="H122" s="3" t="inlineStr">
         <is>
-          <t>31,38</t>
+          <t>27,02</t>
         </is>
       </c>
       <c r="I122" s="2" t="inlineStr">
         <is>
-          <t>545,498</t>
+          <t>542,367</t>
         </is>
       </c>
       <c r="J122" s="2" t="inlineStr">
@@ -29049,17 +29185,17 @@
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/fundos-investimento/mutuos-privatizacao/fmp-fgts-petrobas-4</t>
+          <t>http://www.caixa.gov.br/fundos-investimento/mutuos-privatizacao/fmp-fgts-petrobas-2</t>
         </is>
       </c>
       <c r="L122" s="2" t="inlineStr">
         <is>
-          <t>03.555.959/0001-81</t>
+          <t>03.915.910/0001-92</t>
         </is>
       </c>
       <c r="M122" s="2" t="inlineStr">
         <is>
-          <t>5204</t>
+          <t>5202</t>
         </is>
       </c>
       <c r="N122" s="2" t="inlineStr">
@@ -29069,12 +29205,12 @@
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="P122" s="2" t="inlineStr">
         <is>
-          <t>300.0</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="Q122" s="2" t="inlineStr">
@@ -29119,7 +29255,7 @@
       </c>
       <c r="Y122" s="2" t="inlineStr">
         <is>
-          <t>Fechado para captação</t>
+          <t>Aberto para captação</t>
         </is>
       </c>
       <c r="Z122" s="2" t="inlineStr">
@@ -29132,7 +29268,11 @@
           <t>GERAL</t>
         </is>
       </c>
-      <c r="AB122" s="2" t="inlineStr"/>
+      <c r="AB122" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
       <c r="AC122" s="2" t="inlineStr">
         <is>
           <t>17h00</t>
@@ -29169,52 +29309,53 @@
       </c>
       <c r="AM122" s="2" t="inlineStr">
         <is>
-          <t>CAIXA FUNDO MÚTUO DE PRIVATIZAÇÃO - FGTS - PETROBRAS IV - RESPONSABILIDADE LIMITADA</t>
+          <t>CAIXA FUNDO MÚTUO DE PRIVATIZAÇÃO - FGTS - PETROBRAS II - RESPONSABILIDADE LIMITADA</t>
         </is>
       </c>
       <c r="AN122" s="2" t="inlineStr">
         <is>
-          <t>FUNDO FECHADO.</t>
+          <t>O fundo encontra-se aberto para receber recursos provenientes de outros Fundos FMP-FGTS.
+Prazo de carência: 6 meses para transferência total ou parcial do investimento no FUNDO para outro FMP- FGTS ou para um Clube de Investimento – FGTS, ou 12 meses para retorno à(s) conta(s) vinculada(s) do investidor junto ao FGTS.</t>
         </is>
       </c>
       <c r="AO122" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_5204.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_5202.pdf</t>
         </is>
       </c>
       <c r="AP122" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_5204.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_5202.pdf</t>
         </is>
       </c>
       <c r="AQ122" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_5204.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_5202.pdf</t>
         </is>
       </c>
       <c r="AR122" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_5204.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_5202.pdf</t>
         </is>
       </c>
       <c r="AS122" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5204.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5202.pdf</t>
         </is>
       </c>
       <c r="AT122" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5204.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5202.pdf</t>
         </is>
       </c>
       <c r="AU122" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-termos-adesao/TA_5204.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-termos-adesao/TA_5202.pdf</t>
         </is>
       </c>
       <c r="AV122" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/caixa-asset/sumario-remuneracao/Documents/sumarios/5204-SUMARIO.pdf</t>
+          <t>https://www.caixa.gov.br/caixa-asset/sumario-remuneracao/Documents/sumarios/5202-SUMARIO.pdf</t>
         </is>
       </c>
       <c r="AW122" s="2" t="inlineStr"/>
@@ -29237,32 +29378,32 @@
       </c>
       <c r="D123" s="4" t="inlineStr">
         <is>
-          <t>36,74472500</t>
-        </is>
-      </c>
-      <c r="E123" s="5" t="inlineStr">
-        <is>
-          <t>0,337</t>
+          <t>35,99365000</t>
+        </is>
+      </c>
+      <c r="E123" s="6" t="inlineStr">
+        <is>
+          <t>-2,044</t>
         </is>
       </c>
       <c r="F123" s="6" t="inlineStr">
         <is>
-          <t>-1,74</t>
+          <t>-3,75</t>
         </is>
       </c>
       <c r="G123" s="5" t="inlineStr">
         <is>
-          <t>11,51</t>
+          <t>9,23</t>
         </is>
       </c>
       <c r="H123" s="5" t="inlineStr">
         <is>
-          <t>59,98</t>
+          <t>64,10</t>
         </is>
       </c>
       <c r="I123" s="4" t="inlineStr">
         <is>
-          <t>461,079</t>
+          <t>451,580</t>
         </is>
       </c>
       <c r="J123" s="4" t="inlineStr">
@@ -29460,32 +29601,32 @@
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>41,20026400</t>
+          <t>40,97035900</t>
         </is>
       </c>
       <c r="E124" s="7" t="inlineStr">
         <is>
-          <t>-0,940</t>
+          <t>-0,558</t>
         </is>
       </c>
       <c r="F124" s="7" t="inlineStr">
         <is>
-          <t>-5,79</t>
+          <t>-6,31</t>
         </is>
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>35,29</t>
+          <t>34,54</t>
         </is>
       </c>
       <c r="H124" s="3" t="inlineStr">
         <is>
-          <t>31,69</t>
+          <t>27,32</t>
         </is>
       </c>
       <c r="I124" s="2" t="inlineStr">
         <is>
-          <t>625,423</t>
+          <t>621,643</t>
         </is>
       </c>
       <c r="J124" s="2" t="inlineStr">
@@ -29687,32 +29828,32 @@
       </c>
       <c r="D125" s="4" t="inlineStr">
         <is>
-          <t>1,12868100</t>
+          <t>1,12921100</t>
         </is>
       </c>
       <c r="E125" s="5" t="inlineStr">
         <is>
-          <t>0,047</t>
+          <t>0,046</t>
         </is>
       </c>
       <c r="F125" s="5" t="inlineStr">
         <is>
-          <t>0,51</t>
+          <t>0,56</t>
         </is>
       </c>
       <c r="G125" s="5" t="inlineStr">
         <is>
-          <t>5,49</t>
+          <t>5,54</t>
         </is>
       </c>
       <c r="H125" s="5" t="inlineStr">
         <is>
-          <t>12,86</t>
+          <t>12,88</t>
         </is>
       </c>
       <c r="I125" s="4" t="inlineStr">
         <is>
-          <t>59,525</t>
+          <t>60,000</t>
         </is>
       </c>
       <c r="J125" s="4" t="inlineStr">
@@ -29925,7 +30066,7 @@
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>1,36216100</t>
+          <t>1,36280300</t>
         </is>
       </c>
       <c r="E126" s="3" t="inlineStr">
@@ -29935,12 +30076,12 @@
       </c>
       <c r="F126" s="3" t="inlineStr">
         <is>
-          <t>0,52</t>
+          <t>0,56</t>
         </is>
       </c>
       <c r="G126" s="3" t="inlineStr">
         <is>
-          <t>5,54</t>
+          <t>5,59</t>
         </is>
       </c>
       <c r="H126" s="3" t="inlineStr">
@@ -29950,7 +30091,7 @@
       </c>
       <c r="I126" s="2" t="inlineStr">
         <is>
-          <t>424,250</t>
+          <t>284,712</t>
         </is>
       </c>
       <c r="J126" s="2" t="inlineStr">
@@ -30167,22 +30308,22 @@
       </c>
       <c r="D127" s="4" t="inlineStr">
         <is>
-          <t>5,90944800</t>
+          <t>5,91248200</t>
         </is>
       </c>
       <c r="E127" s="5" t="inlineStr">
         <is>
-          <t>0,052</t>
+          <t>0,051</t>
         </is>
       </c>
       <c r="F127" s="5" t="inlineStr">
         <is>
-          <t>0,56</t>
+          <t>0,61</t>
         </is>
       </c>
       <c r="G127" s="5" t="inlineStr">
         <is>
-          <t>5,94</t>
+          <t>5,99</t>
         </is>
       </c>
       <c r="H127" s="5" t="inlineStr">
@@ -30192,7 +30333,7 @@
       </c>
       <c r="I127" s="4" t="inlineStr">
         <is>
-          <t>41,078</t>
+          <t>41,097</t>
         </is>
       </c>
       <c r="J127" s="4" t="inlineStr">
@@ -30407,7 +30548,7 @@
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>5,14351400</t>
+          <t>5,14617900</t>
         </is>
       </c>
       <c r="E128" s="3" t="inlineStr">
@@ -30417,12 +30558,12 @@
       </c>
       <c r="F128" s="3" t="inlineStr">
         <is>
-          <t>0,57</t>
+          <t>0,62</t>
         </is>
       </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>6,18</t>
+          <t>6,23</t>
         </is>
       </c>
       <c r="H128" s="3" t="inlineStr">
@@ -30432,7 +30573,7 @@
       </c>
       <c r="I128" s="2" t="inlineStr">
         <is>
-          <t>789,237</t>
+          <t>789,645</t>
         </is>
       </c>
       <c r="J128" s="2" t="inlineStr">
@@ -30447,12 +30588,12 @@
       </c>
       <c r="L128" s="2" t="inlineStr">
         <is>
-          <t>09.548.725/0001-93</t>
+          <t>09.181.268/0001-41</t>
         </is>
       </c>
       <c r="M128" s="2" t="inlineStr">
         <is>
-          <t>5132</t>
+          <t>5080</t>
         </is>
       </c>
       <c r="N128" s="2" t="inlineStr">
@@ -30462,12 +30603,12 @@
       </c>
       <c r="O128" s="2" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="P128" s="2" t="inlineStr">
         <is>
-          <t>10000000.0</t>
+          <t>1000.0</t>
         </is>
       </c>
       <c r="Q128" s="2" t="inlineStr">
@@ -30482,7 +30623,7 @@
       </c>
       <c r="S128" s="2" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="T128" s="2" t="inlineStr">
@@ -30522,7 +30663,7 @@
       </c>
       <c r="AA128" s="2" t="inlineStr">
         <is>
-          <t>QUALIFICADO</t>
+          <t>GERAL</t>
         </is>
       </c>
       <c r="AB128" s="2" t="inlineStr">
@@ -30570,7 +30711,7 @@
       </c>
       <c r="AM128" s="2" t="inlineStr">
         <is>
-          <t>CAIXA SAUDE SUPLEMENTAR - ANS II FUNDO DE INVESTIMENTO FINANCEIRO RENDA FIXA LONGO PRAZO - RESPONSABILIDADE LIMITADA</t>
+          <t>CAIXA SAÚDE SUPLEMENTAR - ANS FUNDO DE INVESTIMENTO FINANCEIRO RENDA FIXA LONGO PRAZO - RESPONSABILIDADE LIMITADA</t>
         </is>
       </c>
       <c r="AN128" s="2" t="inlineStr">
@@ -30585,42 +30726,42 @@
       </c>
       <c r="AO128" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_5132.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_5080.pdf</t>
         </is>
       </c>
       <c r="AP128" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_5132.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_5080.pdf</t>
         </is>
       </c>
       <c r="AQ128" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_5132.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_5080.pdf</t>
         </is>
       </c>
       <c r="AR128" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_5132.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_5080.pdf</t>
         </is>
       </c>
       <c r="AS128" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5132.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5080.pdf</t>
         </is>
       </c>
       <c r="AT128" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5132.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5080.pdf</t>
         </is>
       </c>
       <c r="AU128" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-termos-adesao/TA_5132.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-termos-adesao/TA_5080.pdf</t>
         </is>
       </c>
       <c r="AV128" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/caixa-asset/sumario-remuneracao/Documents/sumarios/5132-SUMARIO.pdf</t>
+          <t>https://www.caixa.gov.br/caixa-asset/sumario-remuneracao/Documents/sumarios/5080-SUMARIO.pdf</t>
         </is>
       </c>
       <c r="AW128" s="2" t="inlineStr"/>
@@ -30643,7 +30784,7 @@
       </c>
       <c r="D129" s="4" t="inlineStr">
         <is>
-          <t>3,23096100</t>
+          <t>3,23260400</t>
         </is>
       </c>
       <c r="E129" s="5" t="inlineStr">
@@ -30653,12 +30794,12 @@
       </c>
       <c r="F129" s="5" t="inlineStr">
         <is>
-          <t>0,56</t>
+          <t>0,61</t>
         </is>
       </c>
       <c r="G129" s="5" t="inlineStr">
         <is>
-          <t>6,01</t>
+          <t>6,07</t>
         </is>
       </c>
       <c r="H129" s="5" t="inlineStr">
@@ -30668,7 +30809,7 @@
       </c>
       <c r="I129" s="4" t="inlineStr">
         <is>
-          <t>19,506</t>
+          <t>19,485</t>
         </is>
       </c>
       <c r="J129" s="4" t="inlineStr">
@@ -30884,32 +31025,32 @@
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>23,72045500</t>
+          <t>23,67854600</t>
         </is>
       </c>
       <c r="E130" s="7" t="inlineStr">
         <is>
-          <t>-0,104</t>
+          <t>-0,176</t>
         </is>
       </c>
       <c r="F130" s="7" t="inlineStr">
         <is>
-          <t>-0,13</t>
+          <t>-0,31</t>
         </is>
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t>5,94</t>
+          <t>5,76</t>
         </is>
       </c>
       <c r="H130" s="3" t="inlineStr">
         <is>
-          <t>11,78</t>
+          <t>11,60</t>
         </is>
       </c>
       <c r="I130" s="2" t="inlineStr">
         <is>
-          <t>93,846</t>
+          <t>93,680</t>
         </is>
       </c>
       <c r="J130" s="2" t="inlineStr">
@@ -31127,7 +31268,7 @@
       </c>
       <c r="D131" s="4" t="inlineStr">
         <is>
-          <t>3,28595100</t>
+          <t>3,28763800</t>
         </is>
       </c>
       <c r="E131" s="5" t="inlineStr">
@@ -31137,12 +31278,12 @@
       </c>
       <c r="F131" s="5" t="inlineStr">
         <is>
-          <t>0,56</t>
+          <t>0,61</t>
         </is>
       </c>
       <c r="G131" s="5" t="inlineStr">
         <is>
-          <t>6,06</t>
+          <t>6,12</t>
         </is>
       </c>
       <c r="H131" s="5" t="inlineStr">
@@ -31152,7 +31293,7 @@
       </c>
       <c r="I131" s="4" t="inlineStr">
         <is>
-          <t>8.154,331</t>
+          <t>8.171,557</t>
         </is>
       </c>
       <c r="J131" s="4" t="inlineStr">
@@ -31365,22 +31506,22 @@
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>1.894,40060100</t>
+          <t>1.895,45003600</t>
         </is>
       </c>
       <c r="E132" s="3" t="inlineStr">
         <is>
-          <t>0,056</t>
+          <t>0,055</t>
         </is>
       </c>
       <c r="F132" s="3" t="inlineStr">
         <is>
-          <t>0,62</t>
+          <t>0,67</t>
         </is>
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t>6,42</t>
+          <t>6,48</t>
         </is>
       </c>
       <c r="H132" s="3" t="inlineStr">
@@ -31390,7 +31531,7 @@
       </c>
       <c r="I132" s="2" t="inlineStr">
         <is>
-          <t>16.197,651</t>
+          <t>16.328,793</t>
         </is>
       </c>
       <c r="J132" s="2" t="inlineStr">
@@ -31612,22 +31753,22 @@
       </c>
       <c r="D133" s="4" t="inlineStr">
         <is>
-          <t>4,89801700</t>
+          <t>4,90053500</t>
         </is>
       </c>
       <c r="E133" s="5" t="inlineStr">
         <is>
-          <t>0,050</t>
+          <t>0,051</t>
         </is>
       </c>
       <c r="F133" s="5" t="inlineStr">
         <is>
-          <t>0,54</t>
+          <t>0,59</t>
         </is>
       </c>
       <c r="G133" s="5" t="inlineStr">
         <is>
-          <t>6,23</t>
+          <t>6,28</t>
         </is>
       </c>
       <c r="H133" s="5" t="inlineStr">
@@ -31637,7 +31778,7 @@
       </c>
       <c r="I133" s="4" t="inlineStr">
         <is>
-          <t>3.072,463</t>
+          <t>3.082,789</t>
         </is>
       </c>
       <c r="J133" s="4" t="inlineStr">
@@ -31851,7 +31992,7 @@
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>1,55554400</t>
+          <t>1,55636032</t>
         </is>
       </c>
       <c r="E134" s="3" t="inlineStr">
@@ -31861,12 +32002,12 @@
       </c>
       <c r="F134" s="3" t="inlineStr">
         <is>
-          <t>0,58</t>
+          <t>0,63</t>
         </is>
       </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>6,26</t>
+          <t>6,31</t>
         </is>
       </c>
       <c r="H134" s="3" t="inlineStr">
@@ -31876,7 +32017,7 @@
       </c>
       <c r="I134" s="2" t="inlineStr">
         <is>
-          <t>370,587</t>
+          <t>370,781</t>
         </is>
       </c>
       <c r="J134" s="2" t="inlineStr">
@@ -32074,7 +32215,7 @@
       </c>
       <c r="D135" s="4" t="inlineStr">
         <is>
-          <t>5,14566300</t>
+          <t>5,14838600</t>
         </is>
       </c>
       <c r="E135" s="5" t="inlineStr">
@@ -32084,12 +32225,12 @@
       </c>
       <c r="F135" s="5" t="inlineStr">
         <is>
-          <t>0,58</t>
+          <t>0,63</t>
         </is>
       </c>
       <c r="G135" s="5" t="inlineStr">
         <is>
-          <t>6,29</t>
+          <t>6,34</t>
         </is>
       </c>
       <c r="H135" s="5" t="inlineStr">
@@ -32099,7 +32240,7 @@
       </c>
       <c r="I135" s="4" t="inlineStr">
         <is>
-          <t>286,038</t>
+          <t>286,190</t>
         </is>
       </c>
       <c r="J135" s="4" t="inlineStr">
@@ -32310,7 +32451,7 @@
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>8,74408800</t>
+          <t>8,74848000</t>
         </is>
       </c>
       <c r="E136" s="3" t="inlineStr">
@@ -32320,12 +32461,12 @@
       </c>
       <c r="F136" s="3" t="inlineStr">
         <is>
-          <t>0,54</t>
+          <t>0,59</t>
         </is>
       </c>
       <c r="G136" s="3" t="inlineStr">
         <is>
-          <t>6,18</t>
+          <t>6,23</t>
         </is>
       </c>
       <c r="H136" s="3" t="inlineStr">
@@ -32335,7 +32476,7 @@
       </c>
       <c r="I136" s="2" t="inlineStr">
         <is>
-          <t>3.969,139</t>
+          <t>3.968,917</t>
         </is>
       </c>
       <c r="J136" s="2" t="inlineStr">
@@ -32537,22 +32678,22 @@
       </c>
       <c r="D137" s="4" t="inlineStr">
         <is>
-          <t>17,98661800</t>
+          <t>17,99589400</t>
         </is>
       </c>
       <c r="E137" s="5" t="inlineStr">
         <is>
-          <t>0,050</t>
+          <t>0,051</t>
         </is>
       </c>
       <c r="F137" s="5" t="inlineStr">
         <is>
-          <t>0,55</t>
+          <t>0,60</t>
         </is>
       </c>
       <c r="G137" s="5" t="inlineStr">
         <is>
-          <t>6,24</t>
+          <t>6,29</t>
         </is>
       </c>
       <c r="H137" s="5" t="inlineStr">
@@ -32562,7 +32703,7 @@
       </c>
       <c r="I137" s="4" t="inlineStr">
         <is>
-          <t>4.786,647</t>
+          <t>4.796,116</t>
         </is>
       </c>
       <c r="J137" s="4" t="inlineStr">
@@ -32760,7 +32901,7 @@
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>2,83562300</t>
+          <t>2,83697800</t>
         </is>
       </c>
       <c r="E138" s="3" t="inlineStr">
@@ -32770,12 +32911,12 @@
       </c>
       <c r="F138" s="3" t="inlineStr">
         <is>
-          <t>0,52</t>
+          <t>0,57</t>
         </is>
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t>5,64</t>
+          <t>5,69</t>
         </is>
       </c>
       <c r="H138" s="3" t="inlineStr">
@@ -32785,7 +32926,7 @@
       </c>
       <c r="I138" s="2" t="inlineStr">
         <is>
-          <t>13.598,968</t>
+          <t>13.684,196</t>
         </is>
       </c>
       <c r="J138" s="2" t="inlineStr">
@@ -32998,7 +33139,7 @@
       </c>
       <c r="D139" s="4" t="inlineStr">
         <is>
-          <t>4,44719200</t>
+          <t>4,44954500</t>
         </is>
       </c>
       <c r="E139" s="5" t="inlineStr">
@@ -33008,12 +33149,12 @@
       </c>
       <c r="F139" s="5" t="inlineStr">
         <is>
-          <t>0,58</t>
+          <t>0,63</t>
         </is>
       </c>
       <c r="G139" s="5" t="inlineStr">
         <is>
-          <t>6,31</t>
+          <t>6,36</t>
         </is>
       </c>
       <c r="H139" s="5" t="inlineStr">
@@ -33023,7 +33164,7 @@
       </c>
       <c r="I139" s="4" t="inlineStr">
         <is>
-          <t>13.447,116</t>
+          <t>13.460,727</t>
         </is>
       </c>
       <c r="J139" s="4" t="inlineStr">
@@ -33245,7 +33386,7 @@
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>1,37999400</t>
+          <t>1,38075100</t>
         </is>
       </c>
       <c r="E140" s="3" t="inlineStr">
@@ -33255,12 +33396,12 @@
       </c>
       <c r="F140" s="3" t="inlineStr">
         <is>
-          <t>0,59</t>
+          <t>0,64</t>
         </is>
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>6,37</t>
+          <t>6,43</t>
         </is>
       </c>
       <c r="H140" s="3" t="inlineStr">
@@ -33270,7 +33411,7 @@
       </c>
       <c r="I140" s="2" t="inlineStr">
         <is>
-          <t>3.507,940</t>
+          <t>3.515,079</t>
         </is>
       </c>
       <c r="J140" s="2" t="inlineStr">
@@ -33480,7 +33621,7 @@
       </c>
       <c r="D141" s="4" t="inlineStr">
         <is>
-          <t>1.779,87464500</t>
+          <t>1.780,81442900</t>
         </is>
       </c>
       <c r="E141" s="5" t="inlineStr">
@@ -33490,12 +33631,12 @@
       </c>
       <c r="F141" s="5" t="inlineStr">
         <is>
-          <t>0,58</t>
+          <t>0,63</t>
         </is>
       </c>
       <c r="G141" s="5" t="inlineStr">
         <is>
-          <t>6,21</t>
+          <t>6,27</t>
         </is>
       </c>
       <c r="H141" s="5" t="inlineStr">
@@ -33505,7 +33646,7 @@
       </c>
       <c r="I141" s="4" t="inlineStr">
         <is>
-          <t>1.418,631</t>
+          <t>1.424,033</t>
         </is>
       </c>
       <c r="J141" s="4" t="inlineStr">
@@ -33719,22 +33860,22 @@
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>1,31247400</t>
+          <t>1,31302400</t>
         </is>
       </c>
       <c r="E142" s="3" t="inlineStr">
         <is>
-          <t>0,042</t>
+          <t>0,041</t>
         </is>
       </c>
       <c r="F142" s="3" t="inlineStr">
         <is>
-          <t>0,47</t>
+          <t>0,51</t>
         </is>
       </c>
       <c r="G142" s="3" t="inlineStr">
         <is>
-          <t>5,07</t>
+          <t>5,11</t>
         </is>
       </c>
       <c r="H142" s="3" t="inlineStr">
@@ -33744,7 +33885,7 @@
       </c>
       <c r="I142" s="2" t="inlineStr">
         <is>
-          <t>34.086,510</t>
+          <t>34.099,169</t>
         </is>
       </c>
       <c r="J142" s="2" t="inlineStr">
@@ -33955,22 +34096,22 @@
       </c>
       <c r="D143" s="4" t="inlineStr">
         <is>
-          <t>9,43815600</t>
+          <t>9,44241200</t>
         </is>
       </c>
       <c r="E143" s="5" t="inlineStr">
         <is>
-          <t>0,046</t>
+          <t>0,045</t>
         </is>
       </c>
       <c r="F143" s="5" t="inlineStr">
         <is>
-          <t>0,51</t>
+          <t>0,55</t>
         </is>
       </c>
       <c r="G143" s="5" t="inlineStr">
         <is>
-          <t>5,44</t>
+          <t>5,49</t>
         </is>
       </c>
       <c r="H143" s="5" t="inlineStr">
@@ -33980,7 +34121,7 @@
       </c>
       <c r="I143" s="4" t="inlineStr">
         <is>
-          <t>2.947,663</t>
+          <t>2.931,714</t>
         </is>
       </c>
       <c r="J143" s="4" t="inlineStr">
@@ -34193,7 +34334,7 @@
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>2,48560400</t>
+          <t>2,48676100</t>
         </is>
       </c>
       <c r="E144" s="3" t="inlineStr">
@@ -34203,22 +34344,22 @@
       </c>
       <c r="F144" s="3" t="inlineStr">
         <is>
-          <t>0,51</t>
+          <t>0,55</t>
         </is>
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
-          <t>5,44</t>
+          <t>5,48</t>
         </is>
       </c>
       <c r="H144" s="3" t="inlineStr">
         <is>
-          <t>12,48</t>
+          <t>12,49</t>
         </is>
       </c>
       <c r="I144" s="2" t="inlineStr">
         <is>
-          <t>16.705,991</t>
+          <t>17.179,377</t>
         </is>
       </c>
       <c r="J144" s="2" t="inlineStr">
@@ -34433,22 +34574,22 @@
       </c>
       <c r="D145" s="4" t="inlineStr">
         <is>
-          <t>2,61760700</t>
+          <t>2,61896300</t>
         </is>
       </c>
       <c r="E145" s="5" t="inlineStr">
         <is>
-          <t>0,054</t>
+          <t>0,051</t>
         </is>
       </c>
       <c r="F145" s="5" t="inlineStr">
         <is>
-          <t>0,58</t>
+          <t>0,63</t>
         </is>
       </c>
       <c r="G145" s="5" t="inlineStr">
         <is>
-          <t>6,28</t>
+          <t>6,34</t>
         </is>
       </c>
       <c r="H145" s="5" t="inlineStr">
@@ -34458,7 +34599,7 @@
       </c>
       <c r="I145" s="4" t="inlineStr">
         <is>
-          <t>9.222,983</t>
+          <t>9.186,617</t>
         </is>
       </c>
       <c r="J145" s="4" t="inlineStr">
@@ -34676,32 +34817,32 @@
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>2,40159200</t>
+          <t>2,39681100</t>
         </is>
       </c>
       <c r="E146" s="7" t="inlineStr">
         <is>
-          <t>-0,039</t>
+          <t>-0,199</t>
         </is>
       </c>
       <c r="F146" s="7" t="inlineStr">
         <is>
-          <t>-0,20</t>
+          <t>-0,40</t>
         </is>
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>4,27</t>
+          <t>4,07</t>
         </is>
       </c>
       <c r="H146" s="3" t="inlineStr">
         <is>
-          <t>12,11</t>
+          <t>11,90</t>
         </is>
       </c>
       <c r="I146" s="2" t="inlineStr">
         <is>
-          <t>3.607,274</t>
+          <t>3.595,213</t>
         </is>
       </c>
       <c r="J146" s="2" t="inlineStr">
@@ -34920,32 +35061,32 @@
       </c>
       <c r="D147" s="4" t="inlineStr">
         <is>
-          <t>2,97713400</t>
+          <t>2,97053600</t>
         </is>
       </c>
       <c r="E147" s="6" t="inlineStr">
         <is>
-          <t>-0,136</t>
+          <t>-0,221</t>
         </is>
       </c>
       <c r="F147" s="6" t="inlineStr">
         <is>
-          <t>-0,30</t>
+          <t>-0,52</t>
         </is>
       </c>
       <c r="G147" s="5" t="inlineStr">
         <is>
-          <t>5,57</t>
+          <t>5,33</t>
         </is>
       </c>
       <c r="H147" s="5" t="inlineStr">
         <is>
-          <t>11,47</t>
+          <t>11,25</t>
         </is>
       </c>
       <c r="I147" s="4" t="inlineStr">
         <is>
-          <t>40,073</t>
+          <t>37,608</t>
         </is>
       </c>
       <c r="J147" s="4" t="inlineStr">
@@ -35155,32 +35296,32 @@
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>1.644,20897800</t>
-        </is>
-      </c>
-      <c r="E148" s="3" t="inlineStr">
-        <is>
-          <t>0,022</t>
+          <t>1.643,75687700</t>
+        </is>
+      </c>
+      <c r="E148" s="7" t="inlineStr">
+        <is>
+          <t>-0,027</t>
         </is>
       </c>
       <c r="F148" s="3" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>0,12</t>
         </is>
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>4,76</t>
+          <t>4,73</t>
         </is>
       </c>
       <c r="H148" s="3" t="inlineStr">
         <is>
-          <t>11,77</t>
+          <t>11,76</t>
         </is>
       </c>
       <c r="I148" s="2" t="inlineStr">
         <is>
-          <t>460,013</t>
+          <t>459,886</t>
         </is>
       </c>
       <c r="J148" s="2" t="inlineStr">
@@ -35394,32 +35535,32 @@
       </c>
       <c r="D149" s="4" t="inlineStr">
         <is>
-          <t>4,49303900</t>
+          <t>4,49463900</t>
         </is>
       </c>
       <c r="E149" s="5" t="inlineStr">
         <is>
-          <t>0,048</t>
+          <t>0,035</t>
         </is>
       </c>
       <c r="F149" s="5" t="inlineStr">
         <is>
-          <t>0,50</t>
+          <t>0,54</t>
         </is>
       </c>
       <c r="G149" s="5" t="inlineStr">
         <is>
-          <t>5,89</t>
+          <t>5,92</t>
         </is>
       </c>
       <c r="H149" s="5" t="inlineStr">
         <is>
-          <t>14,12</t>
+          <t>14,10</t>
         </is>
       </c>
       <c r="I149" s="4" t="inlineStr">
         <is>
-          <t>11.040,342</t>
+          <t>11.064,576</t>
         </is>
       </c>
       <c r="J149" s="4" t="inlineStr">
@@ -35640,32 +35781,32 @@
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>3,80580600</t>
+          <t>3,79986600</t>
         </is>
       </c>
       <c r="E150" s="7" t="inlineStr">
         <is>
-          <t>-0,234</t>
+          <t>-0,156</t>
         </is>
       </c>
       <c r="F150" s="7" t="inlineStr">
         <is>
-          <t>-0,35</t>
+          <t>-0,51</t>
         </is>
       </c>
       <c r="G150" s="3" t="inlineStr">
         <is>
-          <t>5,72</t>
+          <t>5,55</t>
         </is>
       </c>
       <c r="H150" s="3" t="inlineStr">
         <is>
-          <t>12,02</t>
+          <t>11,83</t>
         </is>
       </c>
       <c r="I150" s="2" t="inlineStr">
         <is>
-          <t>2.998,999</t>
+          <t>2.995,653</t>
         </is>
       </c>
       <c r="J150" s="2" t="inlineStr">
@@ -35882,32 +36023,32 @@
       </c>
       <c r="D151" s="4" t="inlineStr">
         <is>
-          <t>3,62798700</t>
+          <t>3,61763500</t>
         </is>
       </c>
       <c r="E151" s="6" t="inlineStr">
         <is>
-          <t>-0,025</t>
+          <t>-0,285</t>
         </is>
       </c>
       <c r="F151" s="6" t="inlineStr">
         <is>
-          <t>-0,25</t>
+          <t>-0,53</t>
         </is>
       </c>
       <c r="G151" s="5" t="inlineStr">
         <is>
-          <t>3,92</t>
+          <t>3,62</t>
         </is>
       </c>
       <c r="H151" s="5" t="inlineStr">
         <is>
-          <t>11,92</t>
+          <t>11,70</t>
         </is>
       </c>
       <c r="I151" s="4" t="inlineStr">
         <is>
-          <t>1.733,676</t>
+          <t>1.736,254</t>
         </is>
       </c>
       <c r="J151" s="4" t="inlineStr">
@@ -36128,32 +36269,32 @@
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>5,13689200</t>
+          <t>5,11202800</t>
         </is>
       </c>
       <c r="E152" s="7" t="inlineStr">
         <is>
-          <t>-0,304</t>
+          <t>-0,484</t>
         </is>
       </c>
       <c r="F152" s="7" t="inlineStr">
         <is>
-          <t>-0,57</t>
+          <t>-1,05</t>
         </is>
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
-          <t>4,47</t>
+          <t>3,96</t>
         </is>
       </c>
       <c r="H152" s="3" t="inlineStr">
         <is>
-          <t>9,88</t>
+          <t>9,27</t>
         </is>
       </c>
       <c r="I152" s="2" t="inlineStr">
         <is>
-          <t>2.574,905</t>
+          <t>2.562,092</t>
         </is>
       </c>
       <c r="J152" s="2" t="inlineStr">
@@ -36369,32 +36510,32 @@
       </c>
       <c r="D153" s="4" t="inlineStr">
         <is>
-          <t>5,17469300</t>
+          <t>5,16443500</t>
         </is>
       </c>
       <c r="E153" s="6" t="inlineStr">
         <is>
-          <t>-0,099</t>
+          <t>-0,198</t>
         </is>
       </c>
       <c r="F153" s="6" t="inlineStr">
         <is>
-          <t>-0,13</t>
+          <t>-0,33</t>
         </is>
       </c>
       <c r="G153" s="5" t="inlineStr">
         <is>
-          <t>5,99</t>
+          <t>5,78</t>
         </is>
       </c>
       <c r="H153" s="5" t="inlineStr">
         <is>
-          <t>11,93</t>
+          <t>11,73</t>
         </is>
       </c>
       <c r="I153" s="4" t="inlineStr">
         <is>
-          <t>5.558,139</t>
+          <t>5.547,071</t>
         </is>
       </c>
       <c r="J153" s="4" t="inlineStr">
@@ -36610,32 +36751,32 @@
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>4,75342500</t>
+          <t>4,74624000</t>
         </is>
       </c>
       <c r="E154" s="7" t="inlineStr">
         <is>
-          <t>-0,052</t>
-        </is>
-      </c>
-      <c r="F154" s="3" t="inlineStr">
-        <is>
-          <t>0,10</t>
+          <t>-0,151</t>
+        </is>
+      </c>
+      <c r="F154" s="7" t="inlineStr">
+        <is>
+          <t>-0,04</t>
         </is>
       </c>
       <c r="G154" s="3" t="inlineStr">
         <is>
-          <t>5,31</t>
+          <t>5,15</t>
         </is>
       </c>
       <c r="H154" s="3" t="inlineStr">
         <is>
-          <t>12,90</t>
+          <t>12,70</t>
         </is>
       </c>
       <c r="I154" s="2" t="inlineStr">
         <is>
-          <t>517,528</t>
+          <t>515,746</t>
         </is>
       </c>
       <c r="J154" s="2" t="inlineStr">
@@ -36851,32 +36992,32 @@
       </c>
       <c r="D155" s="4" t="inlineStr">
         <is>
-          <t>7,97734900</t>
+          <t>7,98154500</t>
         </is>
       </c>
       <c r="E155" s="5" t="inlineStr">
         <is>
-          <t>0,049</t>
+          <t>0,052</t>
         </is>
       </c>
       <c r="F155" s="5" t="inlineStr">
         <is>
-          <t>0,53</t>
+          <t>0,58</t>
         </is>
       </c>
       <c r="G155" s="5" t="inlineStr">
         <is>
-          <t>6,17</t>
+          <t>6,22</t>
         </is>
       </c>
       <c r="H155" s="5" t="inlineStr">
         <is>
-          <t>14,47</t>
+          <t>14,48</t>
         </is>
       </c>
       <c r="I155" s="4" t="inlineStr">
         <is>
-          <t>174,708</t>
+          <t>174,260</t>
         </is>
       </c>
       <c r="J155" s="4" t="inlineStr">
@@ -36946,32 +37087,32 @@
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>3,44513200</t>
+          <t>3,41993800</t>
         </is>
       </c>
       <c r="E156" s="7" t="inlineStr">
         <is>
-          <t>-0,451</t>
+          <t>-0,731</t>
         </is>
       </c>
       <c r="F156" s="7" t="inlineStr">
         <is>
-          <t>-0,91</t>
+          <t>-1,64</t>
         </is>
       </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
-          <t>3,26</t>
+          <t>2,50</t>
         </is>
       </c>
       <c r="H156" s="3" t="inlineStr">
         <is>
-          <t>8,30</t>
+          <t>7,38</t>
         </is>
       </c>
       <c r="I156" s="2" t="inlineStr">
         <is>
-          <t>768,628</t>
+          <t>763,007</t>
         </is>
       </c>
       <c r="J156" s="2" t="inlineStr">
@@ -37187,32 +37328,32 @@
       </c>
       <c r="D157" s="4" t="inlineStr">
         <is>
-          <t>3,75318900</t>
+          <t>3,73774600</t>
         </is>
       </c>
       <c r="E157" s="6" t="inlineStr">
         <is>
-          <t>-0,055</t>
+          <t>-0,411</t>
         </is>
       </c>
       <c r="F157" s="6" t="inlineStr">
         <is>
-          <t>-0,54</t>
+          <t>-0,95</t>
         </is>
       </c>
       <c r="G157" s="5" t="inlineStr">
         <is>
-          <t>3,20</t>
+          <t>2,78</t>
         </is>
       </c>
       <c r="H157" s="5" t="inlineStr">
         <is>
-          <t>11,06</t>
+          <t>10,77</t>
         </is>
       </c>
       <c r="I157" s="4" t="inlineStr">
         <is>
-          <t>720,484</t>
+          <t>717,520</t>
         </is>
       </c>
       <c r="J157" s="4" t="inlineStr">
@@ -37433,22 +37574,22 @@
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>7,20087200</t>
+          <t>7,20457600</t>
         </is>
       </c>
       <c r="E158" s="3" t="inlineStr">
         <is>
-          <t>0,050</t>
+          <t>0,051</t>
         </is>
       </c>
       <c r="F158" s="3" t="inlineStr">
         <is>
-          <t>0,54</t>
+          <t>0,60</t>
         </is>
       </c>
       <c r="G158" s="3" t="inlineStr">
         <is>
-          <t>6,21</t>
+          <t>6,26</t>
         </is>
       </c>
       <c r="H158" s="3" t="inlineStr">
@@ -37458,7 +37599,7 @@
       </c>
       <c r="I158" s="2" t="inlineStr">
         <is>
-          <t>12.861,610</t>
+          <t>12.871,038</t>
         </is>
       </c>
       <c r="J158" s="2" t="inlineStr">
@@ -37676,7 +37817,7 @@
       </c>
       <c r="D159" s="4" t="inlineStr">
         <is>
-          <t>7,52212600</t>
+          <t>7,52607600</t>
         </is>
       </c>
       <c r="E159" s="5" t="inlineStr">
@@ -37686,12 +37827,12 @@
       </c>
       <c r="F159" s="5" t="inlineStr">
         <is>
-          <t>0,57</t>
+          <t>0,63</t>
         </is>
       </c>
       <c r="G159" s="5" t="inlineStr">
         <is>
-          <t>6,17</t>
+          <t>6,23</t>
         </is>
       </c>
       <c r="H159" s="5" t="inlineStr">
@@ -37701,7 +37842,7 @@
       </c>
       <c r="I159" s="4" t="inlineStr">
         <is>
-          <t>4.056,296</t>
+          <t>4.058,748</t>
         </is>
       </c>
       <c r="J159" s="4" t="inlineStr">
@@ -37915,32 +38056,32 @@
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>1,44157100</t>
+          <t>1,43811700</t>
         </is>
       </c>
       <c r="E160" s="7" t="inlineStr">
         <is>
-          <t>-0,076</t>
+          <t>-0,239</t>
         </is>
       </c>
       <c r="F160" s="7" t="inlineStr">
         <is>
-          <t>-0,37</t>
+          <t>-0,61</t>
         </is>
       </c>
       <c r="G160" s="3" t="inlineStr">
         <is>
-          <t>3,38</t>
+          <t>3,13</t>
         </is>
       </c>
       <c r="H160" s="3" t="inlineStr">
         <is>
-          <t>11,39</t>
+          <t>11,24</t>
         </is>
       </c>
       <c r="I160" s="2" t="inlineStr">
         <is>
-          <t>169,452</t>
+          <t>169,046</t>
         </is>
       </c>
       <c r="J160" s="2" t="inlineStr">
@@ -38150,22 +38291,22 @@
       </c>
       <c r="D161" s="4" t="inlineStr">
         <is>
-          <t>3,15127000</t>
+          <t>3,15284800</t>
         </is>
       </c>
       <c r="E161" s="5" t="inlineStr">
         <is>
-          <t>0,049</t>
+          <t>0,050</t>
         </is>
       </c>
       <c r="F161" s="5" t="inlineStr">
         <is>
-          <t>0,55</t>
+          <t>0,60</t>
         </is>
       </c>
       <c r="G161" s="5" t="inlineStr">
         <is>
-          <t>5,85</t>
+          <t>5,91</t>
         </is>
       </c>
       <c r="H161" s="5" t="inlineStr">
@@ -38175,7 +38316,7 @@
       </c>
       <c r="I161" s="4" t="inlineStr">
         <is>
-          <t>1.611,368</t>
+          <t>1.635,929</t>
         </is>
       </c>
       <c r="J161" s="4" t="inlineStr">
@@ -38387,22 +38528,22 @@
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>6,74774800</t>
+          <t>6,75138600</t>
         </is>
       </c>
       <c r="E162" s="3" t="inlineStr">
         <is>
-          <t>0,055</t>
+          <t>0,053</t>
         </is>
       </c>
       <c r="F162" s="3" t="inlineStr">
         <is>
-          <t>0,60</t>
+          <t>0,66</t>
         </is>
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
-          <t>6,32</t>
+          <t>6,38</t>
         </is>
       </c>
       <c r="H162" s="3" t="inlineStr">
@@ -38412,7 +38553,7 @@
       </c>
       <c r="I162" s="2" t="inlineStr">
         <is>
-          <t>24.097,819</t>
+          <t>24.070,297</t>
         </is>
       </c>
       <c r="J162" s="2" t="inlineStr">
@@ -38482,32 +38623,32 @@
       </c>
       <c r="D163" s="4" t="inlineStr">
         <is>
-          <t>5,50509900</t>
+          <t>5,47791900</t>
         </is>
       </c>
       <c r="E163" s="6" t="inlineStr">
         <is>
-          <t>-0,305</t>
+          <t>-0,493</t>
         </is>
       </c>
       <c r="F163" s="6" t="inlineStr">
         <is>
-          <t>-0,56</t>
+          <t>-1,05</t>
         </is>
       </c>
       <c r="G163" s="5" t="inlineStr">
         <is>
-          <t>4,73</t>
+          <t>4,21</t>
         </is>
       </c>
       <c r="H163" s="5" t="inlineStr">
         <is>
-          <t>10,07</t>
+          <t>9,40</t>
         </is>
       </c>
       <c r="I163" s="4" t="inlineStr">
         <is>
-          <t>591,385</t>
+          <t>588,415</t>
         </is>
       </c>
       <c r="J163" s="4" t="inlineStr">
@@ -38722,32 +38863,32 @@
       </c>
       <c r="D164" s="2" t="inlineStr">
         <is>
-          <t>1.544,39933900</t>
-        </is>
-      </c>
-      <c r="E164" s="7" t="inlineStr">
-        <is>
-          <t>-0,228</t>
-        </is>
-      </c>
-      <c r="F164" s="7" t="inlineStr">
-        <is>
-          <t>-0,43</t>
-        </is>
-      </c>
-      <c r="G164" s="3" t="inlineStr">
-        <is>
-          <t>4,04</t>
-        </is>
-      </c>
-      <c r="H164" s="3" t="inlineStr">
-        <is>
-          <t>11,88</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E164" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F164" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G164" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H164" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I164" s="2" t="inlineStr">
         <is>
-          <t>129,780</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J164" s="2" t="inlineStr">
@@ -38953,32 +39094,32 @@
       </c>
       <c r="D165" s="4" t="inlineStr">
         <is>
-          <t>3,80634700</t>
+          <t>3,78007900</t>
         </is>
       </c>
       <c r="E165" s="6" t="inlineStr">
         <is>
-          <t>-0,443</t>
+          <t>-0,690</t>
         </is>
       </c>
       <c r="F165" s="6" t="inlineStr">
         <is>
-          <t>-2,34</t>
+          <t>-3,02</t>
         </is>
       </c>
       <c r="G165" s="5" t="inlineStr">
         <is>
-          <t>5,12</t>
+          <t>4,40</t>
         </is>
       </c>
       <c r="H165" s="5" t="inlineStr">
         <is>
-          <t>21,40</t>
+          <t>20,91</t>
         </is>
       </c>
       <c r="I165" s="4" t="inlineStr">
         <is>
-          <t>279,937</t>
+          <t>277,949</t>
         </is>
       </c>
       <c r="J165" s="4" t="inlineStr">
@@ -39188,32 +39329,32 @@
       </c>
       <c r="D166" s="2" t="inlineStr">
         <is>
-          <t>3,49941800</t>
+          <t>3,47570100</t>
         </is>
       </c>
       <c r="E166" s="7" t="inlineStr">
         <is>
-          <t>-0,536</t>
+          <t>-0,677</t>
         </is>
       </c>
       <c r="F166" s="7" t="inlineStr">
         <is>
-          <t>-2,32</t>
+          <t>-2,98</t>
         </is>
       </c>
       <c r="G166" s="3" t="inlineStr">
         <is>
-          <t>4,95</t>
+          <t>4,24</t>
         </is>
       </c>
       <c r="H166" s="3" t="inlineStr">
         <is>
-          <t>20,99</t>
+          <t>20,53</t>
         </is>
       </c>
       <c r="I166" s="2" t="inlineStr">
         <is>
-          <t>8,855</t>
+          <t>8,795</t>
         </is>
       </c>
       <c r="J166" s="2" t="inlineStr">
@@ -39427,32 +39568,32 @@
       </c>
       <c r="D167" s="4" t="inlineStr">
         <is>
-          <t>11,29707500</t>
+          <t>11,22658519</t>
         </is>
       </c>
       <c r="E167" s="6" t="inlineStr">
         <is>
-          <t>-0,369</t>
+          <t>-0,623</t>
         </is>
       </c>
       <c r="F167" s="6" t="inlineStr">
         <is>
-          <t>-1,72</t>
+          <t>-2,33</t>
         </is>
       </c>
       <c r="G167" s="5" t="inlineStr">
         <is>
-          <t>2,08</t>
+          <t>1,44</t>
         </is>
       </c>
       <c r="H167" s="5" t="inlineStr">
         <is>
-          <t>21,88</t>
+          <t>21,72</t>
         </is>
       </c>
       <c r="I167" s="4" t="inlineStr">
         <is>
-          <t>2.324,845</t>
+          <t>2.310,072</t>
         </is>
       </c>
       <c r="J167" s="4" t="inlineStr">
@@ -39666,32 +39807,32 @@
       </c>
       <c r="D168" s="2" t="inlineStr">
         <is>
-          <t>1,96180100</t>
+          <t>1,95004100</t>
         </is>
       </c>
       <c r="E168" s="7" t="inlineStr">
         <is>
-          <t>-0,480</t>
+          <t>-0,599</t>
         </is>
       </c>
       <c r="F168" s="7" t="inlineStr">
         <is>
-          <t>-2,09</t>
+          <t>-2,68</t>
         </is>
       </c>
       <c r="G168" s="3" t="inlineStr">
         <is>
-          <t>3,50</t>
+          <t>2,88</t>
         </is>
       </c>
       <c r="H168" s="3" t="inlineStr">
         <is>
-          <t>18,45</t>
+          <t>18,06</t>
         </is>
       </c>
       <c r="I168" s="2" t="inlineStr">
         <is>
-          <t>193,656</t>
+          <t>192,495</t>
         </is>
       </c>
       <c r="J168" s="2" t="inlineStr">
@@ -39901,32 +40042,32 @@
       </c>
       <c r="D169" s="4" t="inlineStr">
         <is>
-          <t>1,93288000</t>
+          <t>1,90981400</t>
         </is>
       </c>
       <c r="E169" s="6" t="inlineStr">
         <is>
-          <t>-1,074</t>
+          <t>-1,193</t>
         </is>
       </c>
       <c r="F169" s="6" t="inlineStr">
         <is>
-          <t>-3,70</t>
+          <t>-4,85</t>
         </is>
       </c>
       <c r="G169" s="6" t="inlineStr">
         <is>
-          <t>-6,77</t>
+          <t>-7,88</t>
         </is>
       </c>
       <c r="H169" s="5" t="inlineStr">
         <is>
-          <t>6,65</t>
+          <t>5,58</t>
         </is>
       </c>
       <c r="I169" s="4" t="inlineStr">
         <is>
-          <t>729,199</t>
+          <t>720,497</t>
         </is>
       </c>
       <c r="J169" s="4" t="inlineStr">
@@ -40140,32 +40281,32 @@
       </c>
       <c r="D170" s="2" t="inlineStr">
         <is>
-          <t>3,37140500</t>
+          <t>3,35467340</t>
         </is>
       </c>
       <c r="E170" s="7" t="inlineStr">
         <is>
-          <t>-0,401</t>
+          <t>-0,496</t>
         </is>
       </c>
       <c r="F170" s="7" t="inlineStr">
         <is>
-          <t>-1,23</t>
+          <t>-1,72</t>
         </is>
       </c>
       <c r="G170" s="3" t="inlineStr">
         <is>
-          <t>3,63</t>
+          <t>3,11</t>
         </is>
       </c>
       <c r="H170" s="3" t="inlineStr">
         <is>
-          <t>17,07</t>
+          <t>16,12</t>
         </is>
       </c>
       <c r="I170" s="2" t="inlineStr">
         <is>
-          <t>1.292,856</t>
+          <t>1.286,440</t>
         </is>
       </c>
       <c r="J170" s="2" t="inlineStr">
@@ -40371,32 +40512,32 @@
       </c>
       <c r="D171" s="4" t="inlineStr">
         <is>
-          <t>2,43492100</t>
+          <t>2,41697323</t>
         </is>
       </c>
       <c r="E171" s="6" t="inlineStr">
         <is>
-          <t>-0,319</t>
+          <t>-0,737</t>
         </is>
       </c>
       <c r="F171" s="6" t="inlineStr">
         <is>
-          <t>-2,17</t>
+          <t>-2,89</t>
         </is>
       </c>
       <c r="G171" s="5" t="inlineStr">
         <is>
-          <t>3,01</t>
+          <t>2,25</t>
         </is>
       </c>
       <c r="H171" s="5" t="inlineStr">
         <is>
-          <t>17,58</t>
+          <t>16,60</t>
         </is>
       </c>
       <c r="I171" s="4" t="inlineStr">
         <is>
-          <t>745,325</t>
+          <t>739,832</t>
         </is>
       </c>
       <c r="J171" s="4" t="inlineStr">
@@ -40602,32 +40743,32 @@
       </c>
       <c r="D172" s="2" t="inlineStr">
         <is>
-          <t>3,75887300</t>
+          <t>3,76002200</t>
         </is>
       </c>
       <c r="E172" s="3" t="inlineStr">
         <is>
-          <t>0,052</t>
+          <t>0,030</t>
         </is>
       </c>
       <c r="F172" s="3" t="inlineStr">
         <is>
-          <t>0,48</t>
+          <t>0,51</t>
         </is>
       </c>
       <c r="G172" s="3" t="inlineStr">
         <is>
-          <t>5,86</t>
+          <t>5,89</t>
         </is>
       </c>
       <c r="H172" s="3" t="inlineStr">
         <is>
-          <t>14,15</t>
+          <t>14,13</t>
         </is>
       </c>
       <c r="I172" s="2" t="inlineStr">
         <is>
-          <t>5.381,941</t>
+          <t>5.382,581</t>
         </is>
       </c>
       <c r="J172" s="2" t="inlineStr">
